--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_1/epoch_30/per_file_predictions_epoch_30.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_1/epoch_30/per_file_predictions_epoch_30.xlsx
@@ -808,769 +808,769 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.7853,0.0788,0.0907,0.0111</t>
-  </si>
-  <si>
-    <t>0.8010,0.0558,0.0671,0.0162</t>
-  </si>
-  <si>
-    <t>0.9175,0.0261,0.0273,0.0025</t>
-  </si>
-  <si>
-    <t>0.8389,0.0523,0.0636,0.0054</t>
-  </si>
-  <si>
-    <t>0.7036,0.1606,0.0735,0.0168</t>
-  </si>
-  <si>
-    <t>0.7877,0.1149,0.0733,0.0075</t>
-  </si>
-  <si>
-    <t>0.7078,0.1057,0.0423,0.0305</t>
-  </si>
-  <si>
-    <t>0.5548,0.2885,0.0998,0.0203</t>
-  </si>
-  <si>
-    <t>0.7446,0.1389,0.0542,0.0082</t>
-  </si>
-  <si>
-    <t>0.6130,0.2023,0.0521,0.0202</t>
-  </si>
-  <si>
-    <t>0.6432,0.1854,0.0597,0.0195</t>
-  </si>
-  <si>
-    <t>0.8111,0.0914,0.0237,0.0077</t>
-  </si>
-  <si>
-    <t>0.8890,0.0400,0.0481,0.0019</t>
-  </si>
-  <si>
-    <t>0.7560,0.1515,0.1055,0.0028</t>
-  </si>
-  <si>
-    <t>0.8719,0.0502,0.0606,0.0017</t>
-  </si>
-  <si>
-    <t>0.6832,0.0589,0.3764,0.0023</t>
-  </si>
-  <si>
-    <t>0.7543,0.1449,0.1221,0.0031</t>
-  </si>
-  <si>
-    <t>0.3769,0.7302,0.0781,0.0020</t>
-  </si>
-  <si>
-    <t>0.4835,0.5595,0.0996,0.0016</t>
-  </si>
-  <si>
-    <t>0.5464,0.4027,0.1385,0.0079</t>
-  </si>
-  <si>
-    <t>0.2657,0.7684,0.1117,0.0029</t>
-  </si>
-  <si>
-    <t>0.3351,0.6849,0.1425,0.0049</t>
-  </si>
-  <si>
-    <t>0.9081,0.0175,0.0573,0.0013</t>
-  </si>
-  <si>
-    <t>0.8729,0.0273,0.0856,0.0039</t>
-  </si>
-  <si>
-    <t>0.8257,0.0285,0.1514,0.0038</t>
-  </si>
-  <si>
-    <t>0.8111,0.0407,0.1866,0.0022</t>
-  </si>
-  <si>
-    <t>0.7454,0.0468,0.2718,0.0042</t>
-  </si>
-  <si>
-    <t>0.8145,0.0590,0.1196,0.0029</t>
-  </si>
-  <si>
-    <t>0.6629,0.0488,0.3776,0.0020</t>
-  </si>
-  <si>
-    <t>0.7394,0.1896,0.1070,0.0026</t>
-  </si>
-  <si>
-    <t>0.7514,0.1321,0.0842,0.0092</t>
-  </si>
-  <si>
-    <t>0.1474,0.4551,0.7669,0.0085</t>
-  </si>
-  <si>
-    <t>0.4202,0.5908,0.1465,0.0030</t>
-  </si>
-  <si>
-    <t>0.6146,0.2278,0.1027,0.0156</t>
-  </si>
-  <si>
-    <t>0.6505,0.2258,0.1312,0.0118</t>
-  </si>
-  <si>
-    <t>0.6211,0.3146,0.0904,0.0069</t>
-  </si>
-  <si>
-    <t>0.7193,0.2674,0.0826,0.0016</t>
-  </si>
-  <si>
-    <t>0.3787,0.4111,0.2322,0.0269</t>
-  </si>
-  <si>
-    <t>0.9220,0.0065,0.0584,0.0014</t>
-  </si>
-  <si>
-    <t>0.8062,0.0367,0.1810,0.0055</t>
-  </si>
-  <si>
-    <t>0.8519,0.0296,0.1022,0.0058</t>
-  </si>
-  <si>
-    <t>0.9025,0.0099,0.0969,0.0016</t>
-  </si>
-  <si>
-    <t>0.4547,0.4852,0.1414,0.0033</t>
-  </si>
-  <si>
-    <t>0.7383,0.0483,0.3111,0.0031</t>
-  </si>
-  <si>
-    <t>0.8671,0.0356,0.0524,0.0062</t>
-  </si>
-  <si>
-    <t>0.4766,0.6094,0.0735,0.0028</t>
-  </si>
-  <si>
-    <t>0.4762,0.4916,0.1748,0.0030</t>
-  </si>
-  <si>
-    <t>0.5322,0.4176,0.0983,0.0031</t>
-  </si>
-  <si>
-    <t>0.4391,0.1010,0.5232,0.0092</t>
-  </si>
-  <si>
-    <t>0.3103,0.1316,0.6689,0.0061</t>
-  </si>
-  <si>
-    <t>0.8283,0.0236,0.2018,0.0024</t>
-  </si>
-  <si>
-    <t>0.7751,0.0494,0.1827,0.0051</t>
-  </si>
-  <si>
-    <t>0.4759,0.0818,0.6226,0.0052</t>
-  </si>
-  <si>
-    <t>0.7209,0.0501,0.3007,0.0031</t>
-  </si>
-  <si>
-    <t>0.6137,0.2609,0.0763,0.0133</t>
-  </si>
-  <si>
-    <t>0.6195,0.3008,0.0993,0.0081</t>
-  </si>
-  <si>
-    <t>0.7951,0.1159,0.0546,0.0052</t>
-  </si>
-  <si>
-    <t>0.2971,0.2672,0.7023,0.0125</t>
-  </si>
-  <si>
-    <t>0.8274,0.0923,0.0436,0.0049</t>
-  </si>
-  <si>
-    <t>0.7256,0.1199,0.0453,0.0184</t>
-  </si>
-  <si>
-    <t>0.7789,0.1422,0.0430,0.0057</t>
-  </si>
-  <si>
-    <t>0.3536,0.3434,0.3709,0.0033</t>
-  </si>
-  <si>
-    <t>0.4898,0.0741,0.5584,0.0032</t>
-  </si>
-  <si>
-    <t>0.7666,0.0368,0.2708,0.0020</t>
-  </si>
-  <si>
-    <t>0.1016,0.6462,0.6389,0.0037</t>
-  </si>
-  <si>
-    <t>0.6474,0.0439,0.3967,0.0051</t>
-  </si>
-  <si>
-    <t>0.6849,0.2980,0.0913,0.0045</t>
-  </si>
-  <si>
-    <t>0.0174,0.9838,0.0154,0.0003</t>
-  </si>
-  <si>
-    <t>0.8961,0.0435,0.0325,0.0023</t>
-  </si>
-  <si>
-    <t>0.8254,0.0702,0.0431,0.0070</t>
-  </si>
-  <si>
-    <t>0.3074,0.4195,0.5080,0.0068</t>
-  </si>
-  <si>
-    <t>0.1901,0.8091,0.1046,0.0005</t>
-  </si>
-  <si>
-    <t>0.4850,0.3524,0.2207,0.0013</t>
-  </si>
-  <si>
-    <t>0.0261,0.9708,0.0344,0.0001</t>
-  </si>
-  <si>
-    <t>0.3876,0.4207,0.2712,0.0049</t>
-  </si>
-  <si>
-    <t>0.9316,0.0233,0.0311,0.0011</t>
-  </si>
-  <si>
-    <t>0.8501,0.0400,0.0237,0.0116</t>
-  </si>
-  <si>
-    <t>0.9288,0.0164,0.0169,0.0037</t>
-  </si>
-  <si>
-    <t>0.8700,0.0490,0.0526,0.0087</t>
-  </si>
-  <si>
-    <t>0.8594,0.0442,0.0376,0.0062</t>
-  </si>
-  <si>
-    <t>0.8337,0.0368,0.0591,0.0162</t>
-  </si>
-  <si>
-    <t>0.5788,0.1948,0.2639,0.0024</t>
-  </si>
-  <si>
-    <t>0.5618,0.3344,0.1188,0.0045</t>
-  </si>
-  <si>
-    <t>0.4951,0.2984,0.2375,0.0029</t>
-  </si>
-  <si>
-    <t>0.1649,0.7282,0.2644,0.0031</t>
-  </si>
-  <si>
-    <t>0.0725,0.8538,0.4093,0.0016</t>
-  </si>
-  <si>
-    <t>0.5977,0.1899,0.2205,0.0014</t>
-  </si>
-  <si>
-    <t>0.8006,0.1287,0.0484,0.0050</t>
-  </si>
-  <si>
-    <t>0.7504,0.1540,0.0632,0.0058</t>
-  </si>
-  <si>
-    <t>0.6945,0.1667,0.0590,0.0167</t>
-  </si>
-  <si>
-    <t>0.6715,0.2739,0.0518,0.0056</t>
-  </si>
-  <si>
-    <t>0.7422,0.1360,0.0702,0.0091</t>
-  </si>
-  <si>
-    <t>0.7789,0.0750,0.0470,0.0158</t>
-  </si>
-  <si>
-    <t>0.7717,0.1367,0.0443,0.0079</t>
-  </si>
-  <si>
-    <t>0.7500,0.1309,0.0671,0.0100</t>
-  </si>
-  <si>
-    <t>0.8178,0.0703,0.0418,0.0084</t>
-  </si>
-  <si>
-    <t>0.8447,0.0713,0.0319,0.0076</t>
-  </si>
-  <si>
-    <t>0.7269,0.1328,0.0439,0.0167</t>
-  </si>
-  <si>
-    <t>0.8554,0.0504,0.0361,0.0064</t>
-  </si>
-  <si>
-    <t>0.7064,0.1421,0.0643,0.0186</t>
-  </si>
-  <si>
-    <t>0.6348,0.2758,0.1092,0.0069</t>
-  </si>
-  <si>
-    <t>0.8386,0.0613,0.0259,0.0112</t>
-  </si>
-  <si>
-    <t>0.7574,0.1345,0.0573,0.0108</t>
-  </si>
-  <si>
-    <t>0.5990,0.0480,0.5065,0.0023</t>
-  </si>
-  <si>
-    <t>0.7795,0.0453,0.2027,0.0032</t>
-  </si>
-  <si>
-    <t>0.9052,0.0421,0.0395,0.0020</t>
-  </si>
-  <si>
-    <t>0.9039,0.0245,0.0507,0.0024</t>
-  </si>
-  <si>
-    <t>0.4820,0.5491,0.0924,0.0038</t>
-  </si>
-  <si>
-    <t>0.3246,0.6713,0.1480,0.0028</t>
-  </si>
-  <si>
-    <t>0.7107,0.1968,0.0689,0.0068</t>
-  </si>
-  <si>
-    <t>0.7179,0.1537,0.0927,0.0121</t>
-  </si>
-  <si>
-    <t>0.5782,0.4100,0.1043,0.0041</t>
-  </si>
-  <si>
-    <t>0.1999,0.8100,0.1417,0.0026</t>
-  </si>
-  <si>
-    <t>0.7044,0.1994,0.0451,0.0071</t>
-  </si>
-  <si>
-    <t>0.8993,0.0395,0.0481,0.0028</t>
-  </si>
-  <si>
-    <t>0.8235,0.0313,0.1599,0.0034</t>
-  </si>
-  <si>
-    <t>0.7349,0.1599,0.0906,0.0069</t>
-  </si>
-  <si>
-    <t>0.7976,0.0768,0.1056,0.0074</t>
-  </si>
-  <si>
-    <t>0.8058,0.0619,0.0902,0.0066</t>
-  </si>
-  <si>
-    <t>0.5236,0.5283,0.0636,0.0020</t>
-  </si>
-  <si>
-    <t>0.4826,0.5088,0.1393,0.0028</t>
-  </si>
-  <si>
-    <t>0.5540,0.4222,0.1119,0.0041</t>
-  </si>
-  <si>
-    <t>0.0321,0.9416,0.3640,0.0032</t>
-  </si>
-  <si>
-    <t>0.7152,0.2758,0.0644,0.0013</t>
-  </si>
-  <si>
-    <t>0.7629,0.1401,0.0825,0.0045</t>
-  </si>
-  <si>
-    <t>0.6957,0.2134,0.0711,0.0077</t>
-  </si>
-  <si>
-    <t>0.8347,0.0937,0.0403,0.0042</t>
-  </si>
-  <si>
-    <t>0.7063,0.1654,0.0486,0.0113</t>
-  </si>
-  <si>
-    <t>0.7389,0.1352,0.0534,0.0082</t>
-  </si>
-  <si>
-    <t>0.8091,0.1051,0.0641,0.0045</t>
-  </si>
-  <si>
-    <t>0.7591,0.1248,0.0992,0.0071</t>
-  </si>
-  <si>
-    <t>0.8025,0.0654,0.0525,0.0138</t>
-  </si>
-  <si>
-    <t>0.7731,0.0922,0.0704,0.0114</t>
-  </si>
-  <si>
-    <t>0.6690,0.2285,0.0601,0.0071</t>
-  </si>
-  <si>
-    <t>0.4013,0.2694,0.4242,0.0036</t>
-  </si>
-  <si>
-    <t>0.6052,0.3322,0.0954,0.0005</t>
-  </si>
-  <si>
-    <t>0.6933,0.0502,0.3037,0.0023</t>
-  </si>
-  <si>
-    <t>0.6875,0.0898,0.2248,0.0018</t>
-  </si>
-  <si>
-    <t>0.9095,0.0297,0.0416,0.0021</t>
-  </si>
-  <si>
-    <t>0.8430,0.0613,0.0900,0.0018</t>
-  </si>
-  <si>
-    <t>0.7387,0.1322,0.1710,0.0024</t>
-  </si>
-  <si>
-    <t>0.8646,0.0622,0.0625,0.0022</t>
-  </si>
-  <si>
-    <t>0.8748,0.0432,0.0383,0.0079</t>
-  </si>
-  <si>
-    <t>0.8441,0.0339,0.0596,0.0108</t>
-  </si>
-  <si>
-    <t>0.8497,0.0511,0.0331,0.0115</t>
-  </si>
-  <si>
-    <t>0.8711,0.0277,0.0698,0.0044</t>
-  </si>
-  <si>
-    <t>0.3331,0.2251,0.5775,0.0062</t>
-  </si>
-  <si>
-    <t>0.6934,0.1656,0.0582,0.0135</t>
-  </si>
-  <si>
-    <t>0.7777,0.1524,0.0521,0.0042</t>
-  </si>
-  <si>
-    <t>0.8067,0.0683,0.0354,0.0164</t>
-  </si>
-  <si>
-    <t>0.5000,0.5189,0.0708,0.0044</t>
-  </si>
-  <si>
-    <t>0.7095,0.1832,0.0961,0.0099</t>
-  </si>
-  <si>
-    <t>0.6999,0.1906,0.0908,0.0121</t>
-  </si>
-  <si>
-    <t>0.7644,0.0973,0.0462,0.0143</t>
-  </si>
-  <si>
-    <t>0.1655,0.2660,0.7439,0.0234</t>
-  </si>
-  <si>
-    <t>0.8258,0.0523,0.0407,0.0125</t>
-  </si>
-  <si>
-    <t>0.8056,0.0747,0.0437,0.0080</t>
-  </si>
-  <si>
-    <t>0.7267,0.1300,0.0867,0.0109</t>
-  </si>
-  <si>
-    <t>0.8085,0.1284,0.0671,0.0029</t>
-  </si>
-  <si>
-    <t>0.8731,0.0749,0.0359,0.0019</t>
-  </si>
-  <si>
-    <t>0.8385,0.0843,0.0836,0.0027</t>
-  </si>
-  <si>
-    <t>0.8450,0.0901,0.0612,0.0028</t>
-  </si>
-  <si>
-    <t>0.8210,0.1051,0.0417,0.0035</t>
-  </si>
-  <si>
-    <t>0.7788,0.1293,0.0453,0.0070</t>
-  </si>
-  <si>
-    <t>0.7002,0.1832,0.0740,0.0085</t>
-  </si>
-  <si>
-    <t>0.7958,0.0942,0.0526,0.0075</t>
-  </si>
-  <si>
-    <t>0.7523,0.1026,0.0557,0.0130</t>
-  </si>
-  <si>
-    <t>0.8219,0.0952,0.0453,0.0053</t>
-  </si>
-  <si>
-    <t>0.7990,0.1286,0.0477,0.0060</t>
-  </si>
-  <si>
-    <t>0.6713,0.1205,0.0570,0.0298</t>
-  </si>
-  <si>
-    <t>0.7635,0.1311,0.0700,0.0091</t>
-  </si>
-  <si>
-    <t>0.5558,0.3958,0.1155,0.0038</t>
-  </si>
-  <si>
-    <t>0.7288,0.1717,0.0817,0.0060</t>
-  </si>
-  <si>
-    <t>0.7232,0.2617,0.0617,0.0025</t>
-  </si>
-  <si>
-    <t>0.6864,0.2050,0.1601,0.0058</t>
-  </si>
-  <si>
-    <t>0.7054,0.1774,0.0787,0.0129</t>
-  </si>
-  <si>
-    <t>0.7708,0.1333,0.0450,0.0069</t>
-  </si>
-  <si>
-    <t>0.6555,0.2519,0.0893,0.0075</t>
-  </si>
-  <si>
-    <t>0.6926,0.1674,0.1350,0.0121</t>
-  </si>
-  <si>
-    <t>0.1063,0.1825,0.8991,0.0026</t>
-  </si>
-  <si>
-    <t>0.7470,0.1259,0.0832,0.0122</t>
-  </si>
-  <si>
-    <t>0.7028,0.0216,0.3507,0.0049</t>
-  </si>
-  <si>
-    <t>0.6519,0.1727,0.2461,0.0045</t>
-  </si>
-  <si>
-    <t>0.8782,0.0383,0.0890,0.0020</t>
-  </si>
-  <si>
-    <t>0.2233,0.2024,0.7057,0.0083</t>
-  </si>
-  <si>
-    <t>0.7938,0.0319,0.2164,0.0027</t>
-  </si>
-  <si>
-    <t>0.7998,0.0292,0.2255,0.0015</t>
-  </si>
-  <si>
-    <t>0.6260,0.0931,0.4089,0.0018</t>
-  </si>
-  <si>
-    <t>0.8399,0.0667,0.1056,0.0018</t>
-  </si>
-  <si>
-    <t>0.7637,0.0981,0.1273,0.0057</t>
-  </si>
-  <si>
-    <t>0.8014,0.1187,0.0612,0.0034</t>
-  </si>
-  <si>
-    <t>0.8281,0.0943,0.0599,0.0030</t>
-  </si>
-  <si>
-    <t>0.8585,0.0675,0.0778,0.0015</t>
-  </si>
-  <si>
-    <t>0.8020,0.0618,0.1530,0.0025</t>
-  </si>
-  <si>
-    <t>0.8384,0.0531,0.0871,0.0080</t>
-  </si>
-  <si>
-    <t>0.6631,0.2045,0.1301,0.0102</t>
-  </si>
-  <si>
-    <t>0.5611,0.3504,0.1045,0.0124</t>
-  </si>
-  <si>
-    <t>0.6713,0.2581,0.0626,0.0067</t>
-  </si>
-  <si>
-    <t>0.5978,0.3352,0.1270,0.0060</t>
-  </si>
-  <si>
-    <t>0.8518,0.0724,0.0500,0.0026</t>
-  </si>
-  <si>
-    <t>0.7614,0.1147,0.0734,0.0120</t>
-  </si>
-  <si>
-    <t>0.7288,0.1529,0.1345,0.0034</t>
-  </si>
-  <si>
-    <t>0.8352,0.0703,0.0902,0.0024</t>
-  </si>
-  <si>
-    <t>0.8794,0.0343,0.0681,0.0027</t>
-  </si>
-  <si>
-    <t>0.8609,0.0372,0.0593,0.0055</t>
-  </si>
-  <si>
-    <t>0.7983,0.1083,0.1077,0.0039</t>
-  </si>
-  <si>
-    <t>0.7054,0.0629,0.3194,0.0051</t>
-  </si>
-  <si>
-    <t>0.8676,0.0075,0.0949,0.0044</t>
-  </si>
-  <si>
-    <t>0.8794,0.0221,0.0850,0.0052</t>
-  </si>
-  <si>
-    <t>0.9029,0.0205,0.0658,0.0022</t>
-  </si>
-  <si>
-    <t>0.7788,0.0496,0.2177,0.0025</t>
-  </si>
-  <si>
-    <t>0.7249,0.1181,0.0601,0.0225</t>
-  </si>
-  <si>
-    <t>0.6404,0.1690,0.0953,0.0270</t>
-  </si>
-  <si>
-    <t>0.7302,0.1512,0.0573,0.0123</t>
-  </si>
-  <si>
-    <t>0.7077,0.1377,0.0708,0.0125</t>
-  </si>
-  <si>
-    <t>0.8192,0.0646,0.0447,0.0116</t>
-  </si>
-  <si>
-    <t>0.8102,0.1127,0.0604,0.0052</t>
-  </si>
-  <si>
-    <t>0.7050,0.1207,0.0634,0.0214</t>
-  </si>
-  <si>
-    <t>0.7580,0.1066,0.0812,0.0134</t>
-  </si>
-  <si>
-    <t>0.8162,0.0809,0.0465,0.0059</t>
-  </si>
-  <si>
-    <t>0.8325,0.0788,0.0601,0.0028</t>
-  </si>
-  <si>
-    <t>0.8240,0.0648,0.0690,0.0053</t>
-  </si>
-  <si>
-    <t>0.7510,0.0183,0.3640,0.0019</t>
-  </si>
-  <si>
-    <t>0.6464,0.0208,0.4271,0.0048</t>
-  </si>
-  <si>
-    <t>0.7736,0.0255,0.2175,0.0064</t>
-  </si>
-  <si>
-    <t>0.4754,0.0273,0.6897,0.0015</t>
-  </si>
-  <si>
-    <t>0.7747,0.0830,0.1724,0.0051</t>
-  </si>
-  <si>
-    <t>0.4398,0.0536,0.6065,0.0032</t>
-  </si>
-  <si>
-    <t>0.7747,0.0512,0.1880,0.0028</t>
-  </si>
-  <si>
-    <t>0.8224,0.0811,0.1030,0.0015</t>
-  </si>
-  <si>
-    <t>0.8567,0.0335,0.0767,0.0039</t>
-  </si>
-  <si>
-    <t>0.9094,0.0122,0.0582,0.0021</t>
-  </si>
-  <si>
-    <t>0.8541,0.0378,0.0551,0.0063</t>
-  </si>
-  <si>
-    <t>0.8476,0.0528,0.0283,0.0107</t>
-  </si>
-  <si>
-    <t>0.7709,0.1169,0.0550,0.0099</t>
-  </si>
-  <si>
-    <t>0.7652,0.1439,0.0563,0.0081</t>
-  </si>
-  <si>
-    <t>0.6909,0.2105,0.0867,0.0051</t>
-  </si>
-  <si>
-    <t>0.7730,0.1269,0.0275,0.0111</t>
-  </si>
-  <si>
-    <t>0.7051,0.1889,0.0901,0.0118</t>
-  </si>
-  <si>
-    <t>0.6090,0.3042,0.0671,0.0075</t>
-  </si>
-  <si>
-    <t>0.7357,0.1021,0.0662,0.0202</t>
-  </si>
-  <si>
-    <t>0.8275,0.0303,0.1901,0.0018</t>
-  </si>
-  <si>
-    <t>0.8039,0.0702,0.1534,0.0034</t>
-  </si>
-  <si>
-    <t>0.7638,0.0516,0.2033,0.0015</t>
-  </si>
-  <si>
-    <t>0.8255,0.0595,0.0757,0.0062</t>
-  </si>
-  <si>
-    <t>0.8210,0.0234,0.1790,0.0050</t>
-  </si>
-  <si>
-    <t>0.8904,0.0247,0.0572,0.0026</t>
-  </si>
-  <si>
-    <t>0.8302,0.0190,0.1595,0.0032</t>
-  </si>
-  <si>
-    <t>0.8908,0.0184,0.0638,0.0043</t>
-  </si>
-  <si>
-    <t>0.7093,0.1410,0.0944,0.0104</t>
-  </si>
-  <si>
-    <t>0.9169,0.0202,0.0214,0.0040</t>
-  </si>
-  <si>
-    <t>0.8752,0.0379,0.0546,0.0055</t>
-  </si>
-  <si>
-    <t>0.8659,0.0232,0.0375,0.0114</t>
-  </si>
-  <si>
-    <t>0.8790,0.0179,0.0264,0.0126</t>
-  </si>
-  <si>
-    <t>0.8581,0.0393,0.0459,0.0060</t>
+    <t>0.7902,0.1025,0.1297,0.0038</t>
+  </si>
+  <si>
+    <t>0.7901,0.0773,0.0907,0.0100</t>
+  </si>
+  <si>
+    <t>0.8699,0.0468,0.0505,0.0050</t>
+  </si>
+  <si>
+    <t>0.7207,0.1708,0.0732,0.0116</t>
+  </si>
+  <si>
+    <t>0.6791,0.2185,0.0664,0.0091</t>
+  </si>
+  <si>
+    <t>0.8334,0.0557,0.0356,0.0094</t>
+  </si>
+  <si>
+    <t>0.7632,0.0554,0.0490,0.0330</t>
+  </si>
+  <si>
+    <t>0.7716,0.1657,0.0508,0.0038</t>
+  </si>
+  <si>
+    <t>0.7612,0.1028,0.0485,0.0126</t>
+  </si>
+  <si>
+    <t>0.7768,0.1259,0.0687,0.0074</t>
+  </si>
+  <si>
+    <t>0.8165,0.0913,0.0563,0.0073</t>
+  </si>
+  <si>
+    <t>0.7458,0.1157,0.0390,0.0174</t>
+  </si>
+  <si>
+    <t>0.8826,0.0594,0.0407,0.0013</t>
+  </si>
+  <si>
+    <t>0.8300,0.0590,0.1099,0.0031</t>
+  </si>
+  <si>
+    <t>0.8251,0.0892,0.0757,0.0040</t>
+  </si>
+  <si>
+    <t>0.8991,0.0314,0.0774,0.0009</t>
+  </si>
+  <si>
+    <t>0.8037,0.1170,0.0593,0.0052</t>
+  </si>
+  <si>
+    <t>0.1680,0.8473,0.1240,0.0035</t>
+  </si>
+  <si>
+    <t>0.4420,0.5178,0.1626,0.0064</t>
+  </si>
+  <si>
+    <t>0.6548,0.3168,0.0915,0.0055</t>
+  </si>
+  <si>
+    <t>0.0642,0.9426,0.1003,0.0018</t>
+  </si>
+  <si>
+    <t>0.2505,0.7658,0.1833,0.0018</t>
+  </si>
+  <si>
+    <t>0.8197,0.0460,0.1156,0.0067</t>
+  </si>
+  <si>
+    <t>0.8442,0.0480,0.0872,0.0051</t>
+  </si>
+  <si>
+    <t>0.8353,0.0368,0.1595,0.0022</t>
+  </si>
+  <si>
+    <t>0.8704,0.0214,0.0974,0.0044</t>
+  </si>
+  <si>
+    <t>0.8896,0.0192,0.0936,0.0015</t>
+  </si>
+  <si>
+    <t>0.8829,0.0185,0.1098,0.0015</t>
+  </si>
+  <si>
+    <t>0.7581,0.0162,0.3471,0.0017</t>
+  </si>
+  <si>
+    <t>0.6076,0.4279,0.0685,0.0028</t>
+  </si>
+  <si>
+    <t>0.6806,0.2862,0.0864,0.0040</t>
+  </si>
+  <si>
+    <t>0.0468,0.4024,0.9249,0.0068</t>
+  </si>
+  <si>
+    <t>0.7433,0.1434,0.1016,0.0055</t>
+  </si>
+  <si>
+    <t>0.7514,0.1558,0.0714,0.0030</t>
+  </si>
+  <si>
+    <t>0.7789,0.0939,0.0522,0.0129</t>
+  </si>
+  <si>
+    <t>0.8053,0.1073,0.0409,0.0058</t>
+  </si>
+  <si>
+    <t>0.6786,0.2725,0.0699,0.0032</t>
+  </si>
+  <si>
+    <t>0.4831,0.5793,0.0473,0.0035</t>
+  </si>
+  <si>
+    <t>0.7847,0.0249,0.1790,0.0075</t>
+  </si>
+  <si>
+    <t>0.8373,0.0420,0.1426,0.0014</t>
+  </si>
+  <si>
+    <t>0.8661,0.0110,0.0861,0.0044</t>
+  </si>
+  <si>
+    <t>0.6925,0.0488,0.3232,0.0042</t>
+  </si>
+  <si>
+    <t>0.6545,0.3150,0.0554,0.0035</t>
+  </si>
+  <si>
+    <t>0.7921,0.0402,0.2118,0.0029</t>
+  </si>
+  <si>
+    <t>0.8213,0.0597,0.0619,0.0130</t>
+  </si>
+  <si>
+    <t>0.7633,0.1758,0.0799,0.0028</t>
+  </si>
+  <si>
+    <t>0.5126,0.5145,0.1052,0.0015</t>
+  </si>
+  <si>
+    <t>0.4279,0.5990,0.1151,0.0027</t>
+  </si>
+  <si>
+    <t>0.4497,0.0731,0.5410,0.0049</t>
+  </si>
+  <si>
+    <t>0.6282,0.0575,0.3858,0.0049</t>
+  </si>
+  <si>
+    <t>0.9385,0.0176,0.0285,0.0008</t>
+  </si>
+  <si>
+    <t>0.7744,0.0756,0.1580,0.0025</t>
+  </si>
+  <si>
+    <t>0.8191,0.0201,0.2283,0.0013</t>
+  </si>
+  <si>
+    <t>0.7527,0.0283,0.3051,0.0008</t>
+  </si>
+  <si>
+    <t>0.6018,0.3673,0.0914,0.0050</t>
+  </si>
+  <si>
+    <t>0.7416,0.1574,0.0461,0.0093</t>
+  </si>
+  <si>
+    <t>0.5863,0.3484,0.1168,0.0063</t>
+  </si>
+  <si>
+    <t>0.5171,0.2541,0.3575,0.0048</t>
+  </si>
+  <si>
+    <t>0.7366,0.1389,0.0652,0.0141</t>
+  </si>
+  <si>
+    <t>0.5846,0.2981,0.1355,0.0103</t>
+  </si>
+  <si>
+    <t>0.6785,0.2268,0.0983,0.0063</t>
+  </si>
+  <si>
+    <t>0.4654,0.0738,0.5333,0.0036</t>
+  </si>
+  <si>
+    <t>0.5256,0.0437,0.5725,0.0031</t>
+  </si>
+  <si>
+    <t>0.7672,0.0459,0.1940,0.0109</t>
+  </si>
+  <si>
+    <t>0.2273,0.5591,0.3202,0.0009</t>
+  </si>
+  <si>
+    <t>0.6835,0.0336,0.4017,0.0047</t>
+  </si>
+  <si>
+    <t>0.5311,0.5284,0.0669,0.0040</t>
+  </si>
+  <si>
+    <t>0.0033,0.9951,0.0197,0.0002</t>
+  </si>
+  <si>
+    <t>0.8864,0.0594,0.0359,0.0017</t>
+  </si>
+  <si>
+    <t>0.7564,0.1150,0.1073,0.0109</t>
+  </si>
+  <si>
+    <t>0.5738,0.2821,0.2194,0.0049</t>
+  </si>
+  <si>
+    <t>0.2016,0.6888,0.2314,0.0013</t>
+  </si>
+  <si>
+    <t>0.6135,0.2578,0.1833,0.0028</t>
+  </si>
+  <si>
+    <t>0.0086,0.9870,0.0526,0.0001</t>
+  </si>
+  <si>
+    <t>0.5901,0.1921,0.1935,0.0030</t>
+  </si>
+  <si>
+    <t>0.8477,0.0314,0.0427,0.0120</t>
+  </si>
+  <si>
+    <t>0.8900,0.0256,0.0225,0.0074</t>
+  </si>
+  <si>
+    <t>0.8791,0.0241,0.0461,0.0074</t>
+  </si>
+  <si>
+    <t>0.8710,0.0300,0.0365,0.0093</t>
+  </si>
+  <si>
+    <t>0.8689,0.0174,0.0832,0.0036</t>
+  </si>
+  <si>
+    <t>0.7890,0.0714,0.0879,0.0103</t>
+  </si>
+  <si>
+    <t>0.4196,0.3800,0.2627,0.0026</t>
+  </si>
+  <si>
+    <t>0.5099,0.2778,0.2319,0.0041</t>
+  </si>
+  <si>
+    <t>0.6049,0.1841,0.2049,0.0012</t>
+  </si>
+  <si>
+    <t>0.6921,0.0804,0.2623,0.0042</t>
+  </si>
+  <si>
+    <t>0.2744,0.5396,0.3251,0.0032</t>
+  </si>
+  <si>
+    <t>0.7920,0.0701,0.1697,0.0026</t>
+  </si>
+  <si>
+    <t>0.6862,0.1621,0.0719,0.0137</t>
+  </si>
+  <si>
+    <t>0.7348,0.1662,0.0748,0.0076</t>
+  </si>
+  <si>
+    <t>0.7356,0.1120,0.0520,0.0207</t>
+  </si>
+  <si>
+    <t>0.6823,0.1924,0.0701,0.0120</t>
+  </si>
+  <si>
+    <t>0.8255,0.0659,0.0611,0.0081</t>
+  </si>
+  <si>
+    <t>0.8158,0.0816,0.0471,0.0090</t>
+  </si>
+  <si>
+    <t>0.6757,0.1705,0.0697,0.0184</t>
+  </si>
+  <si>
+    <t>0.7293,0.1390,0.0765,0.0112</t>
+  </si>
+  <si>
+    <t>0.7729,0.1359,0.0377,0.0063</t>
+  </si>
+  <si>
+    <t>0.7842,0.1019,0.0582,0.0078</t>
+  </si>
+  <si>
+    <t>0.7902,0.1115,0.0434,0.0103</t>
+  </si>
+  <si>
+    <t>0.7797,0.0989,0.0456,0.0105</t>
+  </si>
+  <si>
+    <t>0.7673,0.1093,0.0527,0.0133</t>
+  </si>
+  <si>
+    <t>0.7012,0.1920,0.0698,0.0083</t>
+  </si>
+  <si>
+    <t>0.7810,0.1090,0.0341,0.0090</t>
+  </si>
+  <si>
+    <t>0.7756,0.1021,0.0385,0.0141</t>
+  </si>
+  <si>
+    <t>0.5818,0.0722,0.4394,0.0023</t>
+  </si>
+  <si>
+    <t>0.7157,0.0794,0.2558,0.0022</t>
+  </si>
+  <si>
+    <t>0.8869,0.0300,0.0906,0.0014</t>
+  </si>
+  <si>
+    <t>0.9104,0.0126,0.0540,0.0020</t>
+  </si>
+  <si>
+    <t>0.5051,0.5434,0.1066,0.0028</t>
+  </si>
+  <si>
+    <t>0.5883,0.4127,0.0961,0.0029</t>
+  </si>
+  <si>
+    <t>0.4346,0.5977,0.0884,0.0031</t>
+  </si>
+  <si>
+    <t>0.3998,0.6141,0.1216,0.0054</t>
+  </si>
+  <si>
+    <t>0.4866,0.5503,0.1004,0.0038</t>
+  </si>
+  <si>
+    <t>0.2556,0.7657,0.1443,0.0039</t>
+  </si>
+  <si>
+    <t>0.5755,0.4292,0.1173,0.0051</t>
+  </si>
+  <si>
+    <t>0.8515,0.0702,0.0510,0.0030</t>
+  </si>
+  <si>
+    <t>0.8343,0.0609,0.0886,0.0039</t>
+  </si>
+  <si>
+    <t>0.8497,0.0639,0.0568,0.0031</t>
+  </si>
+  <si>
+    <t>0.8671,0.0343,0.0534,0.0056</t>
+  </si>
+  <si>
+    <t>0.8730,0.0347,0.0349,0.0076</t>
+  </si>
+  <si>
+    <t>0.4856,0.5144,0.1453,0.0026</t>
+  </si>
+  <si>
+    <t>0.5315,0.4816,0.1159,0.0017</t>
+  </si>
+  <si>
+    <t>0.5698,0.4554,0.0904,0.0014</t>
+  </si>
+  <si>
+    <t>0.0167,0.9788,0.1042,0.0008</t>
+  </si>
+  <si>
+    <t>0.6446,0.2715,0.0767,0.0053</t>
+  </si>
+  <si>
+    <t>0.8197,0.0928,0.0470,0.0045</t>
+  </si>
+  <si>
+    <t>0.7393,0.1761,0.0739,0.0039</t>
+  </si>
+  <si>
+    <t>0.7909,0.1091,0.0652,0.0086</t>
+  </si>
+  <si>
+    <t>0.7999,0.0932,0.0631,0.0084</t>
+  </si>
+  <si>
+    <t>0.6988,0.1731,0.0662,0.0099</t>
+  </si>
+  <si>
+    <t>0.7589,0.1725,0.0614,0.0047</t>
+  </si>
+  <si>
+    <t>0.7124,0.2006,0.0648,0.0090</t>
+  </si>
+  <si>
+    <t>0.7596,0.1301,0.0684,0.0065</t>
+  </si>
+  <si>
+    <t>0.6989,0.1911,0.0872,0.0072</t>
+  </si>
+  <si>
+    <t>0.5405,0.3423,0.1498,0.0102</t>
+  </si>
+  <si>
+    <t>0.4940,0.3307,0.1271,0.0007</t>
+  </si>
+  <si>
+    <t>0.7105,0.2075,0.0860,0.0013</t>
+  </si>
+  <si>
+    <t>0.6743,0.0688,0.2799,0.0021</t>
+  </si>
+  <si>
+    <t>0.8941,0.0114,0.0761,0.0032</t>
+  </si>
+  <si>
+    <t>0.8726,0.0579,0.0549,0.0016</t>
+  </si>
+  <si>
+    <t>0.8203,0.0995,0.0836,0.0020</t>
+  </si>
+  <si>
+    <t>0.7800,0.0845,0.0991,0.0066</t>
+  </si>
+  <si>
+    <t>0.8602,0.0593,0.0611,0.0025</t>
+  </si>
+  <si>
+    <t>0.8707,0.0519,0.0380,0.0051</t>
+  </si>
+  <si>
+    <t>0.8412,0.0318,0.0390,0.0215</t>
+  </si>
+  <si>
+    <t>0.8823,0.0278,0.0295,0.0113</t>
+  </si>
+  <si>
+    <t>0.8182,0.0446,0.0782,0.0114</t>
+  </si>
+  <si>
+    <t>0.1771,0.5948,0.5310,0.0053</t>
+  </si>
+  <si>
+    <t>0.7523,0.1381,0.0486,0.0104</t>
+  </si>
+  <si>
+    <t>0.7044,0.2075,0.0510,0.0066</t>
+  </si>
+  <si>
+    <t>0.7823,0.0812,0.0915,0.0082</t>
+  </si>
+  <si>
+    <t>0.6707,0.2060,0.0776,0.0121</t>
+  </si>
+  <si>
+    <t>0.7362,0.1473,0.0699,0.0118</t>
+  </si>
+  <si>
+    <t>0.7779,0.0912,0.0809,0.0090</t>
+  </si>
+  <si>
+    <t>0.6043,0.3329,0.0827,0.0083</t>
+  </si>
+  <si>
+    <t>0.1741,0.2686,0.7680,0.0136</t>
+  </si>
+  <si>
+    <t>0.7535,0.1326,0.0439,0.0086</t>
+  </si>
+  <si>
+    <t>0.6990,0.1706,0.0489,0.0122</t>
+  </si>
+  <si>
+    <t>0.3193,0.6802,0.1707,0.0067</t>
+  </si>
+  <si>
+    <t>0.8415,0.0804,0.0508,0.0044</t>
+  </si>
+  <si>
+    <t>0.8168,0.1090,0.0795,0.0018</t>
+  </si>
+  <si>
+    <t>0.6012,0.2194,0.1359,0.0261</t>
+  </si>
+  <si>
+    <t>0.8778,0.0601,0.0455,0.0025</t>
+  </si>
+  <si>
+    <t>0.7774,0.1741,0.0446,0.0030</t>
+  </si>
+  <si>
+    <t>0.6773,0.2797,0.0847,0.0061</t>
+  </si>
+  <si>
+    <t>0.7517,0.1152,0.0642,0.0122</t>
+  </si>
+  <si>
+    <t>0.7446,0.1678,0.0973,0.0046</t>
+  </si>
+  <si>
+    <t>0.6774,0.2425,0.1118,0.0077</t>
+  </si>
+  <si>
+    <t>0.6640,0.2105,0.0945,0.0114</t>
+  </si>
+  <si>
+    <t>0.7557,0.1722,0.0386,0.0076</t>
+  </si>
+  <si>
+    <t>0.6424,0.2354,0.1052,0.0121</t>
+  </si>
+  <si>
+    <t>0.7819,0.1158,0.0676,0.0086</t>
+  </si>
+  <si>
+    <t>0.6276,0.2908,0.0838,0.0066</t>
+  </si>
+  <si>
+    <t>0.6771,0.2139,0.1202,0.0055</t>
+  </si>
+  <si>
+    <t>0.7843,0.1014,0.0622,0.0068</t>
+  </si>
+  <si>
+    <t>0.6571,0.2187,0.0737,0.0074</t>
+  </si>
+  <si>
+    <t>0.8521,0.1045,0.0323,0.0039</t>
+  </si>
+  <si>
+    <t>0.8026,0.0857,0.0624,0.0079</t>
+  </si>
+  <si>
+    <t>0.6723,0.2308,0.0672,0.0067</t>
+  </si>
+  <si>
+    <t>0.7316,0.1983,0.0656,0.0059</t>
+  </si>
+  <si>
+    <t>0.1728,0.3178,0.7673,0.0043</t>
+  </si>
+  <si>
+    <t>0.7264,0.1555,0.0606,0.0102</t>
+  </si>
+  <si>
+    <t>0.6951,0.0611,0.3059,0.0042</t>
+  </si>
+  <si>
+    <t>0.7311,0.0438,0.3127,0.0039</t>
+  </si>
+  <si>
+    <t>0.7773,0.0575,0.1918,0.0015</t>
+  </si>
+  <si>
+    <t>0.3091,0.3581,0.4542,0.0044</t>
+  </si>
+  <si>
+    <t>0.8093,0.0308,0.2438,0.0012</t>
+  </si>
+  <si>
+    <t>0.7363,0.0332,0.3570,0.0015</t>
+  </si>
+  <si>
+    <t>0.8462,0.0312,0.1509,0.0015</t>
+  </si>
+  <si>
+    <t>0.7123,0.1266,0.2252,0.0029</t>
+  </si>
+  <si>
+    <t>0.7395,0.1042,0.1887,0.0044</t>
+  </si>
+  <si>
+    <t>0.8504,0.0358,0.1240,0.0018</t>
+  </si>
+  <si>
+    <t>0.9173,0.0290,0.0260,0.0036</t>
+  </si>
+  <si>
+    <t>0.8642,0.0582,0.0732,0.0033</t>
+  </si>
+  <si>
+    <t>0.8743,0.0323,0.0712,0.0030</t>
+  </si>
+  <si>
+    <t>0.7737,0.1249,0.1163,0.0039</t>
+  </si>
+  <si>
+    <t>0.8280,0.0605,0.1201,0.0021</t>
+  </si>
+  <si>
+    <t>0.8066,0.1001,0.0594,0.0056</t>
+  </si>
+  <si>
+    <t>0.5281,0.4543,0.1122,0.0065</t>
+  </si>
+  <si>
+    <t>0.4560,0.4703,0.1905,0.0121</t>
+  </si>
+  <si>
+    <t>0.7207,0.1431,0.0644,0.0093</t>
+  </si>
+  <si>
+    <t>0.6817,0.2344,0.1279,0.0059</t>
+  </si>
+  <si>
+    <t>0.9213,0.0194,0.0474,0.0014</t>
+  </si>
+  <si>
+    <t>0.8974,0.0393,0.0483,0.0011</t>
+  </si>
+  <si>
+    <t>0.9202,0.0131,0.0332,0.0038</t>
+  </si>
+  <si>
+    <t>0.9154,0.0251,0.0419,0.0013</t>
+  </si>
+  <si>
+    <t>0.7815,0.0895,0.1312,0.0055</t>
+  </si>
+  <si>
+    <t>0.4067,0.0921,0.6544,0.0025</t>
+  </si>
+  <si>
+    <t>0.6872,0.0767,0.2845,0.0052</t>
+  </si>
+  <si>
+    <t>0.7389,0.0310,0.3555,0.0026</t>
+  </si>
+  <si>
+    <t>0.8621,0.0322,0.0958,0.0033</t>
+  </si>
+  <si>
+    <t>0.7594,0.0543,0.2210,0.0048</t>
+  </si>
+  <si>
+    <t>0.8399,0.0737,0.0328,0.0061</t>
+  </si>
+  <si>
+    <t>0.7266,0.1589,0.0676,0.0119</t>
+  </si>
+  <si>
+    <t>0.7442,0.1263,0.0497,0.0122</t>
+  </si>
+  <si>
+    <t>0.6389,0.2297,0.1161,0.0111</t>
+  </si>
+  <si>
+    <t>0.6812,0.1973,0.0663,0.0126</t>
+  </si>
+  <si>
+    <t>0.7208,0.1275,0.0955,0.0146</t>
+  </si>
+  <si>
+    <t>0.7993,0.1192,0.0465,0.0050</t>
+  </si>
+  <si>
+    <t>0.7376,0.1482,0.0614,0.0087</t>
+  </si>
+  <si>
+    <t>0.8060,0.0615,0.1047,0.0048</t>
+  </si>
+  <si>
+    <t>0.7931,0.1018,0.0972,0.0045</t>
+  </si>
+  <si>
+    <t>0.7233,0.1466,0.0773,0.0076</t>
+  </si>
+  <si>
+    <t>0.8265,0.0440,0.1235,0.0008</t>
+  </si>
+  <si>
+    <t>0.6031,0.0698,0.3855,0.0104</t>
+  </si>
+  <si>
+    <t>0.7629,0.0708,0.1920,0.0021</t>
+  </si>
+  <si>
+    <t>0.2838,0.0520,0.7933,0.0064</t>
+  </si>
+  <si>
+    <t>0.8273,0.0479,0.1506,0.0012</t>
+  </si>
+  <si>
+    <t>0.3550,0.0428,0.7419,0.0046</t>
+  </si>
+  <si>
+    <t>0.6029,0.0812,0.3690,0.0060</t>
+  </si>
+  <si>
+    <t>0.8527,0.0505,0.0984,0.0029</t>
+  </si>
+  <si>
+    <t>0.9025,0.0175,0.0451,0.0035</t>
+  </si>
+  <si>
+    <t>0.9336,0.0165,0.0413,0.0012</t>
+  </si>
+  <si>
+    <t>0.8795,0.0518,0.0481,0.0023</t>
+  </si>
+  <si>
+    <t>0.7465,0.1884,0.0678,0.0037</t>
+  </si>
+  <si>
+    <t>0.7692,0.1446,0.0448,0.0051</t>
+  </si>
+  <si>
+    <t>0.6326,0.2001,0.0832,0.0167</t>
+  </si>
+  <si>
+    <t>0.6390,0.2688,0.0541,0.0080</t>
+  </si>
+  <si>
+    <t>0.6989,0.1764,0.0806,0.0113</t>
+  </si>
+  <si>
+    <t>0.7267,0.1703,0.0726,0.0063</t>
+  </si>
+  <si>
+    <t>0.7581,0.1242,0.0512,0.0073</t>
+  </si>
+  <si>
+    <t>0.7832,0.1052,0.0379,0.0079</t>
+  </si>
+  <si>
+    <t>0.8227,0.0372,0.1517,0.0019</t>
+  </si>
+  <si>
+    <t>0.5771,0.1027,0.4714,0.0034</t>
+  </si>
+  <si>
+    <t>0.7635,0.0120,0.3418,0.0014</t>
+  </si>
+  <si>
+    <t>0.8306,0.0562,0.1504,0.0021</t>
+  </si>
+  <si>
+    <t>0.5977,0.1139,0.3745,0.0094</t>
+  </si>
+  <si>
+    <t>0.8859,0.0221,0.0643,0.0057</t>
+  </si>
+  <si>
+    <t>0.8123,0.0191,0.2166,0.0019</t>
+  </si>
+  <si>
+    <t>0.8731,0.0159,0.1071,0.0029</t>
+  </si>
+  <si>
+    <t>0.8396,0.0573,0.0357,0.0077</t>
+  </si>
+  <si>
+    <t>0.7791,0.0855,0.0767,0.0116</t>
+  </si>
+  <si>
+    <t>0.8850,0.0317,0.0245,0.0089</t>
+  </si>
+  <si>
+    <t>0.8947,0.0158,0.0339,0.0056</t>
+  </si>
+  <si>
+    <t>0.8571,0.0360,0.0452,0.0080</t>
+  </si>
+  <si>
+    <t>0.8323,0.0863,0.0568,0.0028</t>
   </si>
 </sst>
 </file>
@@ -2401,7 +2401,7 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D34" t="s">
         <v>296</v>
@@ -2471,7 +2471,7 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D39" t="s">
         <v>301</v>
@@ -2583,7 +2583,7 @@
         <v>262</v>
       </c>
       <c r="C47" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D47" t="s">
         <v>309</v>
@@ -2597,7 +2597,7 @@
         <v>262</v>
       </c>
       <c r="C48" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D48" t="s">
         <v>310</v>
@@ -2611,7 +2611,7 @@
         <v>262</v>
       </c>
       <c r="C49" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D49" t="s">
         <v>311</v>
@@ -2639,7 +2639,7 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D51" t="s">
         <v>313</v>
@@ -2681,7 +2681,7 @@
         <v>261</v>
       </c>
       <c r="C54" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D54" t="s">
         <v>316</v>
@@ -2751,7 +2751,7 @@
         <v>261</v>
       </c>
       <c r="C59" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D59" t="s">
         <v>321</v>
@@ -2807,7 +2807,7 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D63" t="s">
         <v>325</v>
@@ -2849,7 +2849,7 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D66" t="s">
         <v>328</v>
@@ -2877,7 +2877,7 @@
         <v>262</v>
       </c>
       <c r="C68" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D68" t="s">
         <v>330</v>
@@ -2933,7 +2933,7 @@
         <v>261</v>
       </c>
       <c r="C72" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D72" t="s">
         <v>334</v>
@@ -3129,7 +3129,7 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D86" t="s">
         <v>348</v>
@@ -3395,7 +3395,7 @@
         <v>261</v>
       </c>
       <c r="C105" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D105" t="s">
         <v>367</v>
@@ -3465,7 +3465,7 @@
         <v>262</v>
       </c>
       <c r="C110" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D110" t="s">
         <v>372</v>
@@ -3479,7 +3479,7 @@
         <v>262</v>
       </c>
       <c r="C111" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D111" t="s">
         <v>373</v>
@@ -3493,7 +3493,7 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D112" t="s">
         <v>374</v>
@@ -3507,7 +3507,7 @@
         <v>262</v>
       </c>
       <c r="C113" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D113" t="s">
         <v>375</v>
@@ -3633,7 +3633,7 @@
         <v>262</v>
       </c>
       <c r="C122" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D122" t="s">
         <v>384</v>
@@ -3997,7 +3997,7 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D148" t="s">
         <v>410</v>
@@ -4053,7 +4053,7 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D152" t="s">
         <v>414</v>
@@ -4151,7 +4151,7 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D159" t="s">
         <v>421</v>
@@ -4529,7 +4529,7 @@
         <v>261</v>
       </c>
       <c r="C186" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D186" t="s">
         <v>448</v>
@@ -4837,7 +4837,7 @@
         <v>261</v>
       </c>
       <c r="C208" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D208" t="s">
         <v>470</v>

--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_1/epoch_30/per_file_predictions_epoch_30.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_1/epoch_30/per_file_predictions_epoch_30.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,772 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.7902,0.1025,0.1297,0.0038</t>
-  </si>
-  <si>
-    <t>0.7901,0.0773,0.0907,0.0100</t>
-  </si>
-  <si>
-    <t>0.8699,0.0468,0.0505,0.0050</t>
-  </si>
-  <si>
-    <t>0.7207,0.1708,0.0732,0.0116</t>
-  </si>
-  <si>
-    <t>0.6791,0.2185,0.0664,0.0091</t>
-  </si>
-  <si>
-    <t>0.8334,0.0557,0.0356,0.0094</t>
-  </si>
-  <si>
-    <t>0.7632,0.0554,0.0490,0.0330</t>
-  </si>
-  <si>
-    <t>0.7716,0.1657,0.0508,0.0038</t>
-  </si>
-  <si>
-    <t>0.7612,0.1028,0.0485,0.0126</t>
-  </si>
-  <si>
-    <t>0.7768,0.1259,0.0687,0.0074</t>
-  </si>
-  <si>
-    <t>0.8165,0.0913,0.0563,0.0073</t>
-  </si>
-  <si>
-    <t>0.7458,0.1157,0.0390,0.0174</t>
-  </si>
-  <si>
-    <t>0.8826,0.0594,0.0407,0.0013</t>
-  </si>
-  <si>
-    <t>0.8300,0.0590,0.1099,0.0031</t>
-  </si>
-  <si>
-    <t>0.8251,0.0892,0.0757,0.0040</t>
-  </si>
-  <si>
-    <t>0.8991,0.0314,0.0774,0.0009</t>
-  </si>
-  <si>
-    <t>0.8037,0.1170,0.0593,0.0052</t>
-  </si>
-  <si>
-    <t>0.1680,0.8473,0.1240,0.0035</t>
-  </si>
-  <si>
-    <t>0.4420,0.5178,0.1626,0.0064</t>
-  </si>
-  <si>
-    <t>0.6548,0.3168,0.0915,0.0055</t>
-  </si>
-  <si>
-    <t>0.0642,0.9426,0.1003,0.0018</t>
-  </si>
-  <si>
-    <t>0.2505,0.7658,0.1833,0.0018</t>
-  </si>
-  <si>
-    <t>0.8197,0.0460,0.1156,0.0067</t>
-  </si>
-  <si>
-    <t>0.8442,0.0480,0.0872,0.0051</t>
-  </si>
-  <si>
-    <t>0.8353,0.0368,0.1595,0.0022</t>
-  </si>
-  <si>
-    <t>0.8704,0.0214,0.0974,0.0044</t>
-  </si>
-  <si>
-    <t>0.8896,0.0192,0.0936,0.0015</t>
-  </si>
-  <si>
-    <t>0.8829,0.0185,0.1098,0.0015</t>
-  </si>
-  <si>
-    <t>0.7581,0.0162,0.3471,0.0017</t>
-  </si>
-  <si>
-    <t>0.6076,0.4279,0.0685,0.0028</t>
-  </si>
-  <si>
-    <t>0.6806,0.2862,0.0864,0.0040</t>
-  </si>
-  <si>
-    <t>0.0468,0.4024,0.9249,0.0068</t>
-  </si>
-  <si>
-    <t>0.7433,0.1434,0.1016,0.0055</t>
-  </si>
-  <si>
-    <t>0.7514,0.1558,0.0714,0.0030</t>
-  </si>
-  <si>
-    <t>0.7789,0.0939,0.0522,0.0129</t>
-  </si>
-  <si>
-    <t>0.8053,0.1073,0.0409,0.0058</t>
-  </si>
-  <si>
-    <t>0.6786,0.2725,0.0699,0.0032</t>
-  </si>
-  <si>
-    <t>0.4831,0.5793,0.0473,0.0035</t>
-  </si>
-  <si>
-    <t>0.7847,0.0249,0.1790,0.0075</t>
-  </si>
-  <si>
-    <t>0.8373,0.0420,0.1426,0.0014</t>
-  </si>
-  <si>
-    <t>0.8661,0.0110,0.0861,0.0044</t>
-  </si>
-  <si>
-    <t>0.6925,0.0488,0.3232,0.0042</t>
-  </si>
-  <si>
-    <t>0.6545,0.3150,0.0554,0.0035</t>
-  </si>
-  <si>
-    <t>0.7921,0.0402,0.2118,0.0029</t>
-  </si>
-  <si>
-    <t>0.8213,0.0597,0.0619,0.0130</t>
-  </si>
-  <si>
-    <t>0.7633,0.1758,0.0799,0.0028</t>
-  </si>
-  <si>
-    <t>0.5126,0.5145,0.1052,0.0015</t>
-  </si>
-  <si>
-    <t>0.4279,0.5990,0.1151,0.0027</t>
-  </si>
-  <si>
-    <t>0.4497,0.0731,0.5410,0.0049</t>
-  </si>
-  <si>
-    <t>0.6282,0.0575,0.3858,0.0049</t>
-  </si>
-  <si>
-    <t>0.9385,0.0176,0.0285,0.0008</t>
-  </si>
-  <si>
-    <t>0.7744,0.0756,0.1580,0.0025</t>
-  </si>
-  <si>
-    <t>0.8191,0.0201,0.2283,0.0013</t>
-  </si>
-  <si>
-    <t>0.7527,0.0283,0.3051,0.0008</t>
-  </si>
-  <si>
-    <t>0.6018,0.3673,0.0914,0.0050</t>
-  </si>
-  <si>
-    <t>0.7416,0.1574,0.0461,0.0093</t>
-  </si>
-  <si>
-    <t>0.5863,0.3484,0.1168,0.0063</t>
-  </si>
-  <si>
-    <t>0.5171,0.2541,0.3575,0.0048</t>
-  </si>
-  <si>
-    <t>0.7366,0.1389,0.0652,0.0141</t>
-  </si>
-  <si>
-    <t>0.5846,0.2981,0.1355,0.0103</t>
-  </si>
-  <si>
-    <t>0.6785,0.2268,0.0983,0.0063</t>
-  </si>
-  <si>
-    <t>0.4654,0.0738,0.5333,0.0036</t>
-  </si>
-  <si>
-    <t>0.5256,0.0437,0.5725,0.0031</t>
-  </si>
-  <si>
-    <t>0.7672,0.0459,0.1940,0.0109</t>
-  </si>
-  <si>
-    <t>0.2273,0.5591,0.3202,0.0009</t>
-  </si>
-  <si>
-    <t>0.6835,0.0336,0.4017,0.0047</t>
-  </si>
-  <si>
-    <t>0.5311,0.5284,0.0669,0.0040</t>
-  </si>
-  <si>
-    <t>0.0033,0.9951,0.0197,0.0002</t>
-  </si>
-  <si>
-    <t>0.8864,0.0594,0.0359,0.0017</t>
-  </si>
-  <si>
-    <t>0.7564,0.1150,0.1073,0.0109</t>
-  </si>
-  <si>
-    <t>0.5738,0.2821,0.2194,0.0049</t>
-  </si>
-  <si>
-    <t>0.2016,0.6888,0.2314,0.0013</t>
-  </si>
-  <si>
-    <t>0.6135,0.2578,0.1833,0.0028</t>
-  </si>
-  <si>
-    <t>0.0086,0.9870,0.0526,0.0001</t>
-  </si>
-  <si>
-    <t>0.5901,0.1921,0.1935,0.0030</t>
-  </si>
-  <si>
-    <t>0.8477,0.0314,0.0427,0.0120</t>
-  </si>
-  <si>
-    <t>0.8900,0.0256,0.0225,0.0074</t>
-  </si>
-  <si>
-    <t>0.8791,0.0241,0.0461,0.0074</t>
-  </si>
-  <si>
-    <t>0.8710,0.0300,0.0365,0.0093</t>
-  </si>
-  <si>
-    <t>0.8689,0.0174,0.0832,0.0036</t>
-  </si>
-  <si>
-    <t>0.7890,0.0714,0.0879,0.0103</t>
-  </si>
-  <si>
-    <t>0.4196,0.3800,0.2627,0.0026</t>
-  </si>
-  <si>
-    <t>0.5099,0.2778,0.2319,0.0041</t>
-  </si>
-  <si>
-    <t>0.6049,0.1841,0.2049,0.0012</t>
-  </si>
-  <si>
-    <t>0.6921,0.0804,0.2623,0.0042</t>
-  </si>
-  <si>
-    <t>0.2744,0.5396,0.3251,0.0032</t>
-  </si>
-  <si>
-    <t>0.7920,0.0701,0.1697,0.0026</t>
-  </si>
-  <si>
-    <t>0.6862,0.1621,0.0719,0.0137</t>
-  </si>
-  <si>
-    <t>0.7348,0.1662,0.0748,0.0076</t>
-  </si>
-  <si>
-    <t>0.7356,0.1120,0.0520,0.0207</t>
-  </si>
-  <si>
-    <t>0.6823,0.1924,0.0701,0.0120</t>
-  </si>
-  <si>
-    <t>0.8255,0.0659,0.0611,0.0081</t>
-  </si>
-  <si>
-    <t>0.8158,0.0816,0.0471,0.0090</t>
-  </si>
-  <si>
-    <t>0.6757,0.1705,0.0697,0.0184</t>
-  </si>
-  <si>
-    <t>0.7293,0.1390,0.0765,0.0112</t>
-  </si>
-  <si>
-    <t>0.7729,0.1359,0.0377,0.0063</t>
-  </si>
-  <si>
-    <t>0.7842,0.1019,0.0582,0.0078</t>
-  </si>
-  <si>
-    <t>0.7902,0.1115,0.0434,0.0103</t>
-  </si>
-  <si>
-    <t>0.7797,0.0989,0.0456,0.0105</t>
-  </si>
-  <si>
-    <t>0.7673,0.1093,0.0527,0.0133</t>
-  </si>
-  <si>
-    <t>0.7012,0.1920,0.0698,0.0083</t>
-  </si>
-  <si>
-    <t>0.7810,0.1090,0.0341,0.0090</t>
-  </si>
-  <si>
-    <t>0.7756,0.1021,0.0385,0.0141</t>
-  </si>
-  <si>
-    <t>0.5818,0.0722,0.4394,0.0023</t>
-  </si>
-  <si>
-    <t>0.7157,0.0794,0.2558,0.0022</t>
-  </si>
-  <si>
-    <t>0.8869,0.0300,0.0906,0.0014</t>
-  </si>
-  <si>
-    <t>0.9104,0.0126,0.0540,0.0020</t>
-  </si>
-  <si>
-    <t>0.5051,0.5434,0.1066,0.0028</t>
-  </si>
-  <si>
-    <t>0.5883,0.4127,0.0961,0.0029</t>
-  </si>
-  <si>
-    <t>0.4346,0.5977,0.0884,0.0031</t>
-  </si>
-  <si>
-    <t>0.3998,0.6141,0.1216,0.0054</t>
-  </si>
-  <si>
-    <t>0.4866,0.5503,0.1004,0.0038</t>
-  </si>
-  <si>
-    <t>0.2556,0.7657,0.1443,0.0039</t>
-  </si>
-  <si>
-    <t>0.5755,0.4292,0.1173,0.0051</t>
-  </si>
-  <si>
-    <t>0.8515,0.0702,0.0510,0.0030</t>
-  </si>
-  <si>
-    <t>0.8343,0.0609,0.0886,0.0039</t>
-  </si>
-  <si>
-    <t>0.8497,0.0639,0.0568,0.0031</t>
-  </si>
-  <si>
-    <t>0.8671,0.0343,0.0534,0.0056</t>
-  </si>
-  <si>
-    <t>0.8730,0.0347,0.0349,0.0076</t>
-  </si>
-  <si>
-    <t>0.4856,0.5144,0.1453,0.0026</t>
-  </si>
-  <si>
-    <t>0.5315,0.4816,0.1159,0.0017</t>
-  </si>
-  <si>
-    <t>0.5698,0.4554,0.0904,0.0014</t>
-  </si>
-  <si>
-    <t>0.0167,0.9788,0.1042,0.0008</t>
-  </si>
-  <si>
-    <t>0.6446,0.2715,0.0767,0.0053</t>
-  </si>
-  <si>
-    <t>0.8197,0.0928,0.0470,0.0045</t>
-  </si>
-  <si>
-    <t>0.7393,0.1761,0.0739,0.0039</t>
-  </si>
-  <si>
-    <t>0.7909,0.1091,0.0652,0.0086</t>
-  </si>
-  <si>
-    <t>0.7999,0.0932,0.0631,0.0084</t>
-  </si>
-  <si>
-    <t>0.6988,0.1731,0.0662,0.0099</t>
-  </si>
-  <si>
-    <t>0.7589,0.1725,0.0614,0.0047</t>
-  </si>
-  <si>
-    <t>0.7124,0.2006,0.0648,0.0090</t>
-  </si>
-  <si>
-    <t>0.7596,0.1301,0.0684,0.0065</t>
-  </si>
-  <si>
-    <t>0.6989,0.1911,0.0872,0.0072</t>
-  </si>
-  <si>
-    <t>0.5405,0.3423,0.1498,0.0102</t>
-  </si>
-  <si>
-    <t>0.4940,0.3307,0.1271,0.0007</t>
-  </si>
-  <si>
-    <t>0.7105,0.2075,0.0860,0.0013</t>
-  </si>
-  <si>
-    <t>0.6743,0.0688,0.2799,0.0021</t>
-  </si>
-  <si>
-    <t>0.8941,0.0114,0.0761,0.0032</t>
-  </si>
-  <si>
-    <t>0.8726,0.0579,0.0549,0.0016</t>
-  </si>
-  <si>
-    <t>0.8203,0.0995,0.0836,0.0020</t>
-  </si>
-  <si>
-    <t>0.7800,0.0845,0.0991,0.0066</t>
-  </si>
-  <si>
-    <t>0.8602,0.0593,0.0611,0.0025</t>
-  </si>
-  <si>
-    <t>0.8707,0.0519,0.0380,0.0051</t>
-  </si>
-  <si>
-    <t>0.8412,0.0318,0.0390,0.0215</t>
-  </si>
-  <si>
-    <t>0.8823,0.0278,0.0295,0.0113</t>
-  </si>
-  <si>
-    <t>0.8182,0.0446,0.0782,0.0114</t>
-  </si>
-  <si>
-    <t>0.1771,0.5948,0.5310,0.0053</t>
-  </si>
-  <si>
-    <t>0.7523,0.1381,0.0486,0.0104</t>
-  </si>
-  <si>
-    <t>0.7044,0.2075,0.0510,0.0066</t>
-  </si>
-  <si>
-    <t>0.7823,0.0812,0.0915,0.0082</t>
-  </si>
-  <si>
-    <t>0.6707,0.2060,0.0776,0.0121</t>
-  </si>
-  <si>
-    <t>0.7362,0.1473,0.0699,0.0118</t>
-  </si>
-  <si>
-    <t>0.7779,0.0912,0.0809,0.0090</t>
-  </si>
-  <si>
-    <t>0.6043,0.3329,0.0827,0.0083</t>
-  </si>
-  <si>
-    <t>0.1741,0.2686,0.7680,0.0136</t>
-  </si>
-  <si>
-    <t>0.7535,0.1326,0.0439,0.0086</t>
-  </si>
-  <si>
-    <t>0.6990,0.1706,0.0489,0.0122</t>
-  </si>
-  <si>
-    <t>0.3193,0.6802,0.1707,0.0067</t>
-  </si>
-  <si>
-    <t>0.8415,0.0804,0.0508,0.0044</t>
-  </si>
-  <si>
-    <t>0.8168,0.1090,0.0795,0.0018</t>
-  </si>
-  <si>
-    <t>0.6012,0.2194,0.1359,0.0261</t>
-  </si>
-  <si>
-    <t>0.8778,0.0601,0.0455,0.0025</t>
-  </si>
-  <si>
-    <t>0.7774,0.1741,0.0446,0.0030</t>
-  </si>
-  <si>
-    <t>0.6773,0.2797,0.0847,0.0061</t>
-  </si>
-  <si>
-    <t>0.7517,0.1152,0.0642,0.0122</t>
-  </si>
-  <si>
-    <t>0.7446,0.1678,0.0973,0.0046</t>
-  </si>
-  <si>
-    <t>0.6774,0.2425,0.1118,0.0077</t>
-  </si>
-  <si>
-    <t>0.6640,0.2105,0.0945,0.0114</t>
-  </si>
-  <si>
-    <t>0.7557,0.1722,0.0386,0.0076</t>
-  </si>
-  <si>
-    <t>0.6424,0.2354,0.1052,0.0121</t>
-  </si>
-  <si>
-    <t>0.7819,0.1158,0.0676,0.0086</t>
-  </si>
-  <si>
-    <t>0.6276,0.2908,0.0838,0.0066</t>
-  </si>
-  <si>
-    <t>0.6771,0.2139,0.1202,0.0055</t>
-  </si>
-  <si>
-    <t>0.7843,0.1014,0.0622,0.0068</t>
-  </si>
-  <si>
-    <t>0.6571,0.2187,0.0737,0.0074</t>
-  </si>
-  <si>
-    <t>0.8521,0.1045,0.0323,0.0039</t>
-  </si>
-  <si>
-    <t>0.8026,0.0857,0.0624,0.0079</t>
-  </si>
-  <si>
-    <t>0.6723,0.2308,0.0672,0.0067</t>
-  </si>
-  <si>
-    <t>0.7316,0.1983,0.0656,0.0059</t>
-  </si>
-  <si>
-    <t>0.1728,0.3178,0.7673,0.0043</t>
-  </si>
-  <si>
-    <t>0.7264,0.1555,0.0606,0.0102</t>
-  </si>
-  <si>
-    <t>0.6951,0.0611,0.3059,0.0042</t>
-  </si>
-  <si>
-    <t>0.7311,0.0438,0.3127,0.0039</t>
-  </si>
-  <si>
-    <t>0.7773,0.0575,0.1918,0.0015</t>
-  </si>
-  <si>
-    <t>0.3091,0.3581,0.4542,0.0044</t>
-  </si>
-  <si>
-    <t>0.8093,0.0308,0.2438,0.0012</t>
-  </si>
-  <si>
-    <t>0.7363,0.0332,0.3570,0.0015</t>
-  </si>
-  <si>
-    <t>0.8462,0.0312,0.1509,0.0015</t>
-  </si>
-  <si>
-    <t>0.7123,0.1266,0.2252,0.0029</t>
-  </si>
-  <si>
-    <t>0.7395,0.1042,0.1887,0.0044</t>
-  </si>
-  <si>
-    <t>0.8504,0.0358,0.1240,0.0018</t>
-  </si>
-  <si>
-    <t>0.9173,0.0290,0.0260,0.0036</t>
-  </si>
-  <si>
-    <t>0.8642,0.0582,0.0732,0.0033</t>
-  </si>
-  <si>
-    <t>0.8743,0.0323,0.0712,0.0030</t>
-  </si>
-  <si>
-    <t>0.7737,0.1249,0.1163,0.0039</t>
-  </si>
-  <si>
-    <t>0.8280,0.0605,0.1201,0.0021</t>
-  </si>
-  <si>
-    <t>0.8066,0.1001,0.0594,0.0056</t>
-  </si>
-  <si>
-    <t>0.5281,0.4543,0.1122,0.0065</t>
-  </si>
-  <si>
-    <t>0.4560,0.4703,0.1905,0.0121</t>
-  </si>
-  <si>
-    <t>0.7207,0.1431,0.0644,0.0093</t>
-  </si>
-  <si>
-    <t>0.6817,0.2344,0.1279,0.0059</t>
-  </si>
-  <si>
-    <t>0.9213,0.0194,0.0474,0.0014</t>
-  </si>
-  <si>
-    <t>0.8974,0.0393,0.0483,0.0011</t>
-  </si>
-  <si>
-    <t>0.9202,0.0131,0.0332,0.0038</t>
-  </si>
-  <si>
-    <t>0.9154,0.0251,0.0419,0.0013</t>
-  </si>
-  <si>
-    <t>0.7815,0.0895,0.1312,0.0055</t>
-  </si>
-  <si>
-    <t>0.4067,0.0921,0.6544,0.0025</t>
-  </si>
-  <si>
-    <t>0.6872,0.0767,0.2845,0.0052</t>
-  </si>
-  <si>
-    <t>0.7389,0.0310,0.3555,0.0026</t>
-  </si>
-  <si>
-    <t>0.8621,0.0322,0.0958,0.0033</t>
-  </si>
-  <si>
-    <t>0.7594,0.0543,0.2210,0.0048</t>
-  </si>
-  <si>
-    <t>0.8399,0.0737,0.0328,0.0061</t>
-  </si>
-  <si>
-    <t>0.7266,0.1589,0.0676,0.0119</t>
-  </si>
-  <si>
-    <t>0.7442,0.1263,0.0497,0.0122</t>
-  </si>
-  <si>
-    <t>0.6389,0.2297,0.1161,0.0111</t>
-  </si>
-  <si>
-    <t>0.6812,0.1973,0.0663,0.0126</t>
-  </si>
-  <si>
-    <t>0.7208,0.1275,0.0955,0.0146</t>
-  </si>
-  <si>
-    <t>0.7993,0.1192,0.0465,0.0050</t>
-  </si>
-  <si>
-    <t>0.7376,0.1482,0.0614,0.0087</t>
-  </si>
-  <si>
-    <t>0.8060,0.0615,0.1047,0.0048</t>
-  </si>
-  <si>
-    <t>0.7931,0.1018,0.0972,0.0045</t>
-  </si>
-  <si>
-    <t>0.7233,0.1466,0.0773,0.0076</t>
-  </si>
-  <si>
-    <t>0.8265,0.0440,0.1235,0.0008</t>
-  </si>
-  <si>
-    <t>0.6031,0.0698,0.3855,0.0104</t>
-  </si>
-  <si>
-    <t>0.7629,0.0708,0.1920,0.0021</t>
-  </si>
-  <si>
-    <t>0.2838,0.0520,0.7933,0.0064</t>
-  </si>
-  <si>
-    <t>0.8273,0.0479,0.1506,0.0012</t>
-  </si>
-  <si>
-    <t>0.3550,0.0428,0.7419,0.0046</t>
-  </si>
-  <si>
-    <t>0.6029,0.0812,0.3690,0.0060</t>
-  </si>
-  <si>
-    <t>0.8527,0.0505,0.0984,0.0029</t>
-  </si>
-  <si>
-    <t>0.9025,0.0175,0.0451,0.0035</t>
-  </si>
-  <si>
-    <t>0.9336,0.0165,0.0413,0.0012</t>
-  </si>
-  <si>
-    <t>0.8795,0.0518,0.0481,0.0023</t>
-  </si>
-  <si>
-    <t>0.7465,0.1884,0.0678,0.0037</t>
-  </si>
-  <si>
-    <t>0.7692,0.1446,0.0448,0.0051</t>
-  </si>
-  <si>
-    <t>0.6326,0.2001,0.0832,0.0167</t>
-  </si>
-  <si>
-    <t>0.6390,0.2688,0.0541,0.0080</t>
-  </si>
-  <si>
-    <t>0.6989,0.1764,0.0806,0.0113</t>
-  </si>
-  <si>
-    <t>0.7267,0.1703,0.0726,0.0063</t>
-  </si>
-  <si>
-    <t>0.7581,0.1242,0.0512,0.0073</t>
-  </si>
-  <si>
-    <t>0.7832,0.1052,0.0379,0.0079</t>
-  </si>
-  <si>
-    <t>0.8227,0.0372,0.1517,0.0019</t>
-  </si>
-  <si>
-    <t>0.5771,0.1027,0.4714,0.0034</t>
-  </si>
-  <si>
-    <t>0.7635,0.0120,0.3418,0.0014</t>
-  </si>
-  <si>
-    <t>0.8306,0.0562,0.1504,0.0021</t>
-  </si>
-  <si>
-    <t>0.5977,0.1139,0.3745,0.0094</t>
-  </si>
-  <si>
-    <t>0.8859,0.0221,0.0643,0.0057</t>
-  </si>
-  <si>
-    <t>0.8123,0.0191,0.2166,0.0019</t>
-  </si>
-  <si>
-    <t>0.8731,0.0159,0.1071,0.0029</t>
-  </si>
-  <si>
-    <t>0.8396,0.0573,0.0357,0.0077</t>
-  </si>
-  <si>
-    <t>0.7791,0.0855,0.0767,0.0116</t>
-  </si>
-  <si>
-    <t>0.8850,0.0317,0.0245,0.0089</t>
-  </si>
-  <si>
-    <t>0.8947,0.0158,0.0339,0.0056</t>
-  </si>
-  <si>
-    <t>0.8571,0.0360,0.0452,0.0080</t>
-  </si>
-  <si>
-    <t>0.8323,0.0863,0.0568,0.0028</t>
+    <t>0,1,0,1</t>
+  </si>
+  <si>
+    <t>0.9703,0.0080,0.0055,0.0074</t>
+  </si>
+  <si>
+    <t>0.0163,0.0018,0.0010,0.9930</t>
+  </si>
+  <si>
+    <t>0.9407,0.0035,0.0014,0.0487</t>
+  </si>
+  <si>
+    <t>0.6553,0.0064,0.0351,0.3042</t>
+  </si>
+  <si>
+    <t>0.9915,0.0031,0.0014,0.0016</t>
+  </si>
+  <si>
+    <t>0.9915,0.0046,0.0004,0.0010</t>
+  </si>
+  <si>
+    <t>0.9939,0.0012,0.0003,0.0022</t>
+  </si>
+  <si>
+    <t>0.9957,0.0005,0.0006,0.0011</t>
+  </si>
+  <si>
+    <t>0.9807,0.0073,0.0011,0.0058</t>
+  </si>
+  <si>
+    <t>0.9772,0.0127,0.0012,0.0055</t>
+  </si>
+  <si>
+    <t>0.9822,0.0111,0.0023,0.0029</t>
+  </si>
+  <si>
+    <t>0.9961,0.0003,0.0001,0.0023</t>
+  </si>
+  <si>
+    <t>0.8020,0.0753,0.1272,0.0113</t>
+  </si>
+  <si>
+    <t>0.5085,0.0675,0.4500,0.0080</t>
+  </si>
+  <si>
+    <t>0.7687,0.0366,0.2306,0.0112</t>
+  </si>
+  <si>
+    <t>0.0607,0.0132,0.9456,0.0024</t>
+  </si>
+  <si>
+    <t>0.9343,0.0223,0.0205,0.0174</t>
+  </si>
+  <si>
+    <t>0.0004,0.9985,0.0040,0.0004</t>
+  </si>
+  <si>
+    <t>0.0005,0.9981,0.0014,0.0014</t>
+  </si>
+  <si>
+    <t>0.0858,0.9201,0.0135,0.0021</t>
+  </si>
+  <si>
+    <t>0.0005,0.9983,0.0019,0.0005</t>
+  </si>
+  <si>
+    <t>0.0010,0.9971,0.0016,0.0014</t>
+  </si>
+  <si>
+    <t>0.4751,0.0298,0.3966,0.1115</t>
+  </si>
+  <si>
+    <t>0.5308,0.2402,0.2283,0.1290</t>
+  </si>
+  <si>
+    <t>0.0010,0.0011,0.9864,0.0309</t>
+  </si>
+  <si>
+    <t>0.4559,0.0102,0.6655,0.0120</t>
+  </si>
+  <si>
+    <t>0.0814,0.0082,0.9481,0.0076</t>
+  </si>
+  <si>
+    <t>0.0588,0.0090,0.8813,0.1216</t>
+  </si>
+  <si>
+    <t>0.0007,0.0011,0.9943,0.0109</t>
+  </si>
+  <si>
+    <t>0.0510,0.9416,0.0145,0.0123</t>
+  </si>
+  <si>
+    <t>0.3309,0.0776,0.6862,0.0137</t>
+  </si>
+  <si>
+    <t>0.0045,0.0113,0.9941,0.0025</t>
+  </si>
+  <si>
+    <t>0.0044,0.9770,0.0561,0.0004</t>
+  </si>
+  <si>
+    <t>0.7521,0.0530,0.0329,0.1194</t>
+  </si>
+  <si>
+    <t>0.4455,0.0572,0.6176,0.0219</t>
+  </si>
+  <si>
+    <t>0.7983,0.2004,0.0164,0.0112</t>
+  </si>
+  <si>
+    <t>0.0244,0.9672,0.0557,0.0019</t>
+  </si>
+  <si>
+    <t>0.0431,0.7629,0.4183,0.0614</t>
+  </si>
+  <si>
+    <t>0.0079,0.0025,0.9501,0.0483</t>
+  </si>
+  <si>
+    <t>0.0338,0.0365,0.9570,0.0091</t>
+  </si>
+  <si>
+    <t>0.0569,0.0033,0.9483,0.0159</t>
+  </si>
+  <si>
+    <t>0.0084,0.2884,0.9629,0.0036</t>
+  </si>
+  <si>
+    <t>0.0151,0.9679,0.0233,0.0043</t>
+  </si>
+  <si>
+    <t>0.0136,0.0169,0.9753,0.0087</t>
+  </si>
+  <si>
+    <t>0.0855,0.7296,0.0087,0.4852</t>
+  </si>
+  <si>
+    <t>0.0021,0.9895,0.0129,0.0084</t>
+  </si>
+  <si>
+    <t>0.0005,0.9965,0.0239,0.0005</t>
+  </si>
+  <si>
+    <t>0.0011,0.9952,0.0578,0.0004</t>
+  </si>
+  <si>
+    <t>0.0011,0.0379,0.9862,0.0102</t>
+  </si>
+  <si>
+    <t>0.0045,0.1403,0.9762,0.0071</t>
+  </si>
+  <si>
+    <t>0.3629,0.0210,0.7576,0.0064</t>
+  </si>
+  <si>
+    <t>0.1062,0.0064,0.9254,0.0153</t>
+  </si>
+  <si>
+    <t>0.0014,0.0029,0.9785,0.0677</t>
+  </si>
+  <si>
+    <t>0.0066,0.0115,0.9826,0.0138</t>
+  </si>
+  <si>
+    <t>0.9692,0.0175,0.0030,0.0084</t>
+  </si>
+  <si>
+    <t>0.9503,0.0093,0.0302,0.0093</t>
+  </si>
+  <si>
+    <t>0.9772,0.0131,0.0029,0.0046</t>
+  </si>
+  <si>
+    <t>0.0458,0.1946,0.9243,0.0375</t>
+  </si>
+  <si>
+    <t>0.9926,0.0012,0.0004,0.0036</t>
+  </si>
+  <si>
+    <t>0.9872,0.0076,0.0015,0.0027</t>
+  </si>
+  <si>
+    <t>0.8892,0.1293,0.0019,0.0046</t>
+  </si>
+  <si>
+    <t>0.0009,0.8704,0.9800,0.0004</t>
+  </si>
+  <si>
+    <t>0.0167,0.1635,0.9594,0.0053</t>
+  </si>
+  <si>
+    <t>0.0013,0.0394,0.9904,0.0049</t>
+  </si>
+  <si>
+    <t>0.0004,0.9821,0.9541,0.0001</t>
+  </si>
+  <si>
+    <t>0.0007,0.0108,0.9967,0.0017</t>
+  </si>
+  <si>
+    <t>0.0093,0.9783,0.0351,0.0014</t>
+  </si>
+  <si>
+    <t>0.0094,0.9846,0.0101,0.0003</t>
+  </si>
+  <si>
+    <t>0.8820,0.0190,0.1113,0.0105</t>
+  </si>
+  <si>
+    <t>0.4202,0.0977,0.6648,0.0136</t>
+  </si>
+  <si>
+    <t>0.0275,0.0339,0.9600,0.0398</t>
+  </si>
+  <si>
+    <t>0.0032,0.9314,0.8995,0.0010</t>
+  </si>
+  <si>
+    <t>0.0011,0.9853,0.6618,0.0002</t>
+  </si>
+  <si>
+    <t>0.0020,0.9920,0.0192,0.0008</t>
+  </si>
+  <si>
+    <t>0.0023,0.9424,0.8866,0.0009</t>
+  </si>
+  <si>
+    <t>0.0075,0.0017,0.1085,0.9678</t>
+  </si>
+  <si>
+    <t>0.0040,0.0018,0.0012,0.9970</t>
+  </si>
+  <si>
+    <t>0.0006,0.0360,0.0011,0.9982</t>
+  </si>
+  <si>
+    <t>0.0014,0.0007,0.0012,0.9988</t>
+  </si>
+  <si>
+    <t>0.0171,0.0099,0.0206,0.9784</t>
+  </si>
+  <si>
+    <t>0.0030,0.0034,0.0023,0.9968</t>
+  </si>
+  <si>
+    <t>0.0022,0.9237,0.9363,0.0006</t>
+  </si>
+  <si>
+    <t>0.0091,0.6397,0.9177,0.0041</t>
+  </si>
+  <si>
+    <t>0.0158,0.6615,0.8492,0.0058</t>
+  </si>
+  <si>
+    <t>0.0119,0.3809,0.9427,0.0031</t>
+  </si>
+  <si>
+    <t>0.0006,0.9753,0.8921,0.0002</t>
+  </si>
+  <si>
+    <t>0.0123,0.9128,0.4321,0.0027</t>
+  </si>
+  <si>
+    <t>0.9974,0.0003,0.0001,0.0012</t>
+  </si>
+  <si>
+    <t>0.9859,0.0183,0.0005,0.0007</t>
+  </si>
+  <si>
+    <t>0.9883,0.0037,0.0004,0.0036</t>
+  </si>
+  <si>
+    <t>0.9892,0.0039,0.0008,0.0019</t>
+  </si>
+  <si>
+    <t>0.9913,0.0067,0.0007,0.0010</t>
+  </si>
+  <si>
+    <t>0.9912,0.0025,0.0008,0.0019</t>
+  </si>
+  <si>
+    <t>0.9878,0.0071,0.0011,0.0016</t>
+  </si>
+  <si>
+    <t>0.9805,0.0090,0.0027,0.0039</t>
+  </si>
+  <si>
+    <t>0.9976,0.0005,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9972,0.0006,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9952,0.0003,0.0001,0.0024</t>
+  </si>
+  <si>
+    <t>0.9970,0.0005,0.0001,0.0008</t>
+  </si>
+  <si>
+    <t>0.9950,0.0009,0.0002,0.0013</t>
+  </si>
+  <si>
+    <t>0.9892,0.0026,0.0007,0.0035</t>
+  </si>
+  <si>
+    <t>0.9864,0.0032,0.0015,0.0048</t>
+  </si>
+  <si>
+    <t>0.9939,0.0014,0.0006,0.0013</t>
+  </si>
+  <si>
+    <t>0.0004,0.0035,0.9947,0.0157</t>
+  </si>
+  <si>
+    <t>0.0189,0.0131,0.9814,0.0036</t>
+  </si>
+  <si>
+    <t>0.8767,0.0129,0.0158,0.0620</t>
+  </si>
+  <si>
+    <t>0.0451,0.0081,0.9718,0.0036</t>
+  </si>
+  <si>
+    <t>0.0064,0.9882,0.0039,0.0018</t>
+  </si>
+  <si>
+    <t>0.0040,0.9922,0.0077,0.0012</t>
+  </si>
+  <si>
+    <t>0.0432,0.9490,0.0090,0.0048</t>
+  </si>
+  <si>
+    <t>0.0101,0.9853,0.0031,0.0024</t>
+  </si>
+  <si>
+    <t>0.0039,0.9906,0.0055,0.0021</t>
+  </si>
+  <si>
+    <t>0.0111,0.9825,0.0069,0.0008</t>
+  </si>
+  <si>
+    <t>0.5994,0.5245,0.0061,0.0024</t>
+  </si>
+  <si>
+    <t>0.8506,0.0511,0.0928,0.0142</t>
+  </si>
+  <si>
+    <t>0.2512,0.0102,0.8485,0.0101</t>
+  </si>
+  <si>
+    <t>0.3119,0.0872,0.3989,0.3226</t>
+  </si>
+  <si>
+    <t>0.5465,0.0297,0.3194,0.1010</t>
+  </si>
+  <si>
+    <t>0.0238,0.5152,0.0308,0.8371</t>
+  </si>
+  <si>
+    <t>0.0008,0.9945,0.0283,0.0023</t>
+  </si>
+  <si>
+    <t>0.0009,0.9893,0.0051,0.0199</t>
+  </si>
+  <si>
+    <t>0.0241,0.9535,0.0247,0.0108</t>
+  </si>
+  <si>
+    <t>0.0009,0.9920,0.2895,0.0006</t>
+  </si>
+  <si>
+    <t>0.0125,0.9807,0.0521,0.0004</t>
+  </si>
+  <si>
+    <t>0.8422,0.1953,0.0209,0.0025</t>
+  </si>
+  <si>
+    <t>0.3701,0.6744,0.0038,0.0131</t>
+  </si>
+  <si>
+    <t>0.9860,0.0051,0.0014,0.0030</t>
+  </si>
+  <si>
+    <t>0.9838,0.0018,0.0006,0.0107</t>
+  </si>
+  <si>
+    <t>0.9803,0.0023,0.0005,0.0128</t>
+  </si>
+  <si>
+    <t>0.9816,0.0044,0.0022,0.0060</t>
+  </si>
+  <si>
+    <t>0.9977,0.0001,0.0000,0.0024</t>
+  </si>
+  <si>
+    <t>0.9812,0.0080,0.0022,0.0052</t>
+  </si>
+  <si>
+    <t>0.9931,0.0013,0.0004,0.0026</t>
+  </si>
+  <si>
+    <t>0.9700,0.0095,0.0062,0.0073</t>
+  </si>
+  <si>
+    <t>0.0091,0.7377,0.8044,0.0064</t>
+  </si>
+  <si>
+    <t>0.0065,0.8897,0.8360,0.0027</t>
+  </si>
+  <si>
+    <t>0.0033,0.3914,0.9659,0.0007</t>
+  </si>
+  <si>
+    <t>0.0851,0.0200,0.9231,0.0122</t>
+  </si>
+  <si>
+    <t>0.9143,0.0164,0.0535,0.0049</t>
+  </si>
+  <si>
+    <t>0.6993,0.0195,0.3926,0.0053</t>
+  </si>
+  <si>
+    <t>0.3630,0.0042,0.5856,0.0610</t>
+  </si>
+  <si>
+    <t>0.6419,0.0792,0.3615,0.0144</t>
+  </si>
+  <si>
+    <t>0.0241,0.0146,0.0046,0.9825</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0014,0.9996</t>
+  </si>
+  <si>
+    <t>0.0005,0.0067,0.0005,0.9991</t>
+  </si>
+  <si>
+    <t>0.0023,0.0011,0.0013,0.9979</t>
+  </si>
+  <si>
+    <t>0.0021,0.8543,0.9251,0.0026</t>
+  </si>
+  <si>
+    <t>0.9909,0.0017,0.0007,0.0037</t>
+  </si>
+  <si>
+    <t>0.0865,0.8889,0.0153,0.0514</t>
+  </si>
+  <si>
+    <t>0.9663,0.0082,0.0029,0.0224</t>
+  </si>
+  <si>
+    <t>0.3720,0.6968,0.0180,0.0117</t>
+  </si>
+  <si>
+    <t>0.9914,0.0015,0.0017,0.0016</t>
+  </si>
+  <si>
+    <t>0.8988,0.0136,0.0232,0.0527</t>
+  </si>
+  <si>
+    <t>0.9776,0.0036,0.0014,0.0103</t>
+  </si>
+  <si>
+    <t>0.0070,0.1287,0.9713,0.0142</t>
+  </si>
+  <si>
+    <t>0.9147,0.0009,0.0034,0.0835</t>
+  </si>
+  <si>
+    <t>0.9001,0.0081,0.0046,0.0782</t>
+  </si>
+  <si>
+    <t>0.7640,0.3039,0.0144,0.0104</t>
+  </si>
+  <si>
+    <t>0.9037,0.0365,0.0334,0.0169</t>
+  </si>
+  <si>
+    <t>0.9726,0.0151,0.0054,0.0031</t>
+  </si>
+  <si>
+    <t>0.2598,0.6481,0.1141,0.0202</t>
+  </si>
+  <si>
+    <t>0.8374,0.0240,0.1591,0.0049</t>
+  </si>
+  <si>
+    <t>0.8062,0.2019,0.0361,0.0061</t>
+  </si>
+  <si>
+    <t>0.9823,0.0013,0.0007,0.0150</t>
+  </si>
+  <si>
+    <t>0.9863,0.0026,0.0009,0.0055</t>
+  </si>
+  <si>
+    <t>0.9854,0.0020,0.0011,0.0061</t>
+  </si>
+  <si>
+    <t>0.9888,0.0005,0.0007,0.0079</t>
+  </si>
+  <si>
+    <t>0.9783,0.0072,0.0030,0.0074</t>
+  </si>
+  <si>
+    <t>0.9900,0.0014,0.0016,0.0031</t>
+  </si>
+  <si>
+    <t>0.9918,0.0024,0.0012,0.0021</t>
+  </si>
+  <si>
+    <t>0.9950,0.0005,0.0003,0.0023</t>
+  </si>
+  <si>
+    <t>0.7161,0.2743,0.0120,0.0114</t>
+  </si>
+  <si>
+    <t>0.5890,0.4253,0.0234,0.0021</t>
+  </si>
+  <si>
+    <t>0.3736,0.6716,0.0163,0.0024</t>
+  </si>
+  <si>
+    <t>0.9244,0.0255,0.0315,0.0135</t>
+  </si>
+  <si>
+    <t>0.9903,0.0051,0.0004,0.0010</t>
+  </si>
+  <si>
+    <t>0.9748,0.0157,0.0018,0.0027</t>
+  </si>
+  <si>
+    <t>0.9832,0.0104,0.0013,0.0032</t>
+  </si>
+  <si>
+    <t>0.9706,0.0209,0.0014,0.0051</t>
+  </si>
+  <si>
+    <t>0.0071,0.0102,0.9947,0.0010</t>
+  </si>
+  <si>
+    <t>0.9702,0.0136,0.0057,0.0070</t>
+  </si>
+  <si>
+    <t>0.0023,0.0021,0.9947,0.0038</t>
+  </si>
+  <si>
+    <t>0.0089,0.0087,0.9360,0.1096</t>
+  </si>
+  <si>
+    <t>0.0092,0.0024,0.9905,0.0026</t>
+  </si>
+  <si>
+    <t>0.0133,0.2741,0.9383,0.0143</t>
+  </si>
+  <si>
+    <t>0.0149,0.0086,0.9857,0.0018</t>
+  </si>
+  <si>
+    <t>0.0189,0.0025,0.9715,0.0207</t>
+  </si>
+  <si>
+    <t>0.0067,0.0143,0.9851,0.0079</t>
+  </si>
+  <si>
+    <t>0.1395,0.0167,0.8701,0.0347</t>
+  </si>
+  <si>
+    <t>0.4482,0.0162,0.6980,0.0067</t>
+  </si>
+  <si>
+    <t>0.4417,0.0282,0.6495,0.0231</t>
+  </si>
+  <si>
+    <t>0.3049,0.3750,0.3745,0.0311</t>
+  </si>
+  <si>
+    <t>0.4876,0.0632,0.5394,0.0141</t>
+  </si>
+  <si>
+    <t>0.6656,0.2011,0.1230,0.0270</t>
+  </si>
+  <si>
+    <t>0.4838,0.3077,0.3554,0.0339</t>
+  </si>
+  <si>
+    <t>0.5534,0.0333,0.5169,0.0177</t>
+  </si>
+  <si>
+    <t>0.2193,0.8388,0.0075,0.0024</t>
+  </si>
+  <si>
+    <t>0.3243,0.7685,0.0053,0.0034</t>
+  </si>
+  <si>
+    <t>0.7013,0.4726,0.0030,0.0022</t>
+  </si>
+  <si>
+    <t>0.8745,0.1480,0.0055,0.0069</t>
+  </si>
+  <si>
+    <t>0.4220,0.6891,0.0022,0.0035</t>
+  </si>
+  <si>
+    <t>0.8485,0.0227,0.0482,0.0505</t>
+  </si>
+  <si>
+    <t>0.9439,0.0037,0.0488,0.0028</t>
+  </si>
+  <si>
+    <t>0.8240,0.0132,0.0390,0.0697</t>
+  </si>
+  <si>
+    <t>0.8236,0.0056,0.2506,0.0019</t>
+  </si>
+  <si>
+    <t>0.4774,0.0158,0.3120,0.1331</t>
+  </si>
+  <si>
+    <t>0.0077,0.0063,0.9788,0.0253</t>
+  </si>
+  <si>
+    <t>0.0301,0.0990,0.8751,0.0726</t>
+  </si>
+  <si>
+    <t>0.0347,0.0649,0.9197,0.0408</t>
+  </si>
+  <si>
+    <t>0.0079,0.0146,0.9819,0.0049</t>
+  </si>
+  <si>
+    <t>0.0121,0.0857,0.9235,0.0213</t>
+  </si>
+  <si>
+    <t>0.9844,0.0013,0.0002,0.0101</t>
+  </si>
+  <si>
+    <t>0.9829,0.0104,0.0024,0.0035</t>
+  </si>
+  <si>
+    <t>0.9776,0.0074,0.0008,0.0074</t>
+  </si>
+  <si>
+    <t>0.9145,0.1241,0.0034,0.0042</t>
+  </si>
+  <si>
+    <t>0.9833,0.0044,0.0015,0.0076</t>
+  </si>
+  <si>
+    <t>0.9934,0.0016,0.0004,0.0022</t>
+  </si>
+  <si>
+    <t>0.9941,0.0012,0.0004,0.0017</t>
+  </si>
+  <si>
+    <t>0.9909,0.0051,0.0010,0.0016</t>
+  </si>
+  <si>
+    <t>0.3726,0.0039,0.8051,0.0063</t>
+  </si>
+  <si>
+    <t>0.1996,0.2134,0.7289,0.0117</t>
+  </si>
+  <si>
+    <t>0.8834,0.0230,0.0726,0.0183</t>
+  </si>
+  <si>
+    <t>0.0290,0.0168,0.9720,0.0049</t>
+  </si>
+  <si>
+    <t>0.0006,0.0010,0.9650,0.1841</t>
+  </si>
+  <si>
+    <t>0.0240,0.0356,0.9410,0.0230</t>
+  </si>
+  <si>
+    <t>0.0030,0.0030,0.9954,0.0029</t>
+  </si>
+  <si>
+    <t>0.0178,0.0332,0.9667,0.0067</t>
+  </si>
+  <si>
+    <t>0.0008,0.0032,0.9889,0.0199</t>
+  </si>
+  <si>
+    <t>0.0094,0.0117,0.9807,0.0064</t>
+  </si>
+  <si>
+    <t>0.0381,0.1673,0.8214,0.0248</t>
+  </si>
+  <si>
+    <t>0.5356,0.0162,0.5095,0.0324</t>
+  </si>
+  <si>
+    <t>0.8039,0.0257,0.1966,0.0166</t>
+  </si>
+  <si>
+    <t>0.9026,0.0169,0.0234,0.0406</t>
+  </si>
+  <si>
+    <t>0.9881,0.0078,0.0005,0.0015</t>
+  </si>
+  <si>
+    <t>0.9922,0.0030,0.0004,0.0015</t>
+  </si>
+  <si>
+    <t>0.9899,0.0031,0.0007,0.0029</t>
+  </si>
+  <si>
+    <t>0.9870,0.0068,0.0016,0.0022</t>
+  </si>
+  <si>
+    <t>0.9953,0.0008,0.0001,0.0015</t>
+  </si>
+  <si>
+    <t>0.9900,0.0065,0.0005,0.0013</t>
+  </si>
+  <si>
+    <t>0.9873,0.0160,0.0012,0.0008</t>
+  </si>
+  <si>
+    <t>0.9849,0.0066,0.0005,0.0034</t>
+  </si>
+  <si>
+    <t>0.0077,0.0134,0.9798,0.0088</t>
+  </si>
+  <si>
+    <t>0.0008,0.4056,0.9829,0.0007</t>
+  </si>
+  <si>
+    <t>0.0197,0.0272,0.9674,0.0072</t>
+  </si>
+  <si>
+    <t>0.1146,0.0209,0.8836,0.0141</t>
+  </si>
+  <si>
+    <t>0.0058,0.0085,0.9877,0.0045</t>
+  </si>
+  <si>
+    <t>0.3542,0.0185,0.5663,0.1066</t>
+  </si>
+  <si>
+    <t>0.3379,0.1559,0.6188,0.0655</t>
+  </si>
+  <si>
+    <t>0.2044,0.2146,0.6208,0.1074</t>
+  </si>
+  <si>
+    <t>0.9560,0.0014,0.0015,0.0423</t>
+  </si>
+  <si>
+    <t>0.1472,0.0163,0.0060,0.9134</t>
+  </si>
+  <si>
+    <t>0.0726,0.0082,0.0032,0.9697</t>
+  </si>
+  <si>
+    <t>0.0023,0.0009,0.0006,0.9985</t>
+  </si>
+  <si>
+    <t>0.0025,0.0007,0.0005,0.9983</t>
+  </si>
+  <si>
+    <t>0.8725,0.0099,0.0117,0.1004</t>
   </si>
 </sst>
 </file>
@@ -1956,7 +1959,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1967,10 +1970,10 @@
         <v>260</v>
       </c>
       <c r="C3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,7 +1987,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1998,7 +2001,7 @@
         <v>259</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2012,7 +2015,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2026,7 +2029,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2040,7 +2043,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2054,7 +2057,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2068,7 +2071,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2082,7 +2085,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2096,7 +2099,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2110,7 +2113,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2124,7 +2127,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2138,7 +2141,7 @@
         <v>259</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2152,7 +2155,7 @@
         <v>259</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2163,10 +2166,10 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2180,7 +2183,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2194,7 +2197,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2208,7 +2211,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2219,10 +2222,10 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2236,7 +2239,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2250,7 +2253,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,7 +2267,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2278,7 +2281,7 @@
         <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2289,10 +2292,10 @@
         <v>261</v>
       </c>
       <c r="C26" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2303,10 +2306,10 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2317,10 +2320,10 @@
         <v>261</v>
       </c>
       <c r="C28" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2331,10 +2334,10 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2345,10 +2348,10 @@
         <v>261</v>
       </c>
       <c r="C30" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2359,10 +2362,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2373,10 +2376,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2390,7 +2393,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2401,10 +2404,10 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2418,7 +2421,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2429,10 +2432,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2446,7 +2449,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2457,10 +2460,10 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2474,7 +2477,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2485,10 +2488,10 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2499,10 +2502,10 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2513,10 +2516,10 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2527,10 +2530,10 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2541,10 +2544,10 @@
         <v>262</v>
       </c>
       <c r="C44" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2555,10 +2558,10 @@
         <v>261</v>
       </c>
       <c r="C45" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2569,10 +2572,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2583,10 +2586,10 @@
         <v>262</v>
       </c>
       <c r="C47" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2600,7 +2603,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2614,7 +2617,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2628,7 +2631,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2639,10 +2642,10 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2653,10 +2656,10 @@
         <v>261</v>
       </c>
       <c r="C52" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2667,10 +2670,10 @@
         <v>261</v>
       </c>
       <c r="C53" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2681,10 +2684,10 @@
         <v>261</v>
       </c>
       <c r="C54" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2695,10 +2698,10 @@
         <v>261</v>
       </c>
       <c r="C55" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2712,7 +2715,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2726,7 +2729,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2740,7 +2743,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2751,10 +2754,10 @@
         <v>261</v>
       </c>
       <c r="C59" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2768,7 +2771,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2782,7 +2785,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2796,7 +2799,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2807,10 +2810,10 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2824,7 +2827,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2835,10 +2838,10 @@
         <v>261</v>
       </c>
       <c r="C65" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2849,10 +2852,10 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2863,10 +2866,10 @@
         <v>261</v>
       </c>
       <c r="C67" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2880,7 +2883,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2897,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2908,7 +2911,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2919,10 +2922,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2933,10 +2936,10 @@
         <v>261</v>
       </c>
       <c r="C72" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2947,10 +2950,10 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2961,10 +2964,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2978,7 +2981,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2989,10 +2992,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3003,10 +3006,10 @@
         <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3017,10 +3020,10 @@
         <v>260</v>
       </c>
       <c r="C78" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3031,10 +3034,10 @@
         <v>260</v>
       </c>
       <c r="C79" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3045,10 +3048,10 @@
         <v>260</v>
       </c>
       <c r="C80" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3059,10 +3062,10 @@
         <v>260</v>
       </c>
       <c r="C81" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3073,10 +3076,10 @@
         <v>260</v>
       </c>
       <c r="C82" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3087,10 +3090,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3101,10 +3104,10 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3115,10 +3118,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3129,10 +3132,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3143,10 +3146,10 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3157,10 +3160,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3174,7 +3177,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3188,7 +3191,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3202,7 +3205,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3216,7 +3219,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3230,7 +3233,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3244,7 +3247,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3258,7 +3261,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3272,7 +3275,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,7 +3289,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3300,7 +3303,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3314,7 +3317,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3331,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3342,7 +3345,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3356,7 +3359,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3370,7 +3373,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,7 +3387,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3395,10 +3398,10 @@
         <v>261</v>
       </c>
       <c r="C105" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3409,10 +3412,10 @@
         <v>261</v>
       </c>
       <c r="C106" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,7 +3429,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3437,10 +3440,10 @@
         <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3454,7 +3457,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3465,10 +3468,10 @@
         <v>262</v>
       </c>
       <c r="C110" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3482,7 +3485,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3496,7 +3499,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3510,7 +3513,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3524,7 +3527,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3535,10 +3538,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3552,7 +3555,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3563,10 +3566,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3580,7 +3583,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3594,7 +3597,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3605,10 +3608,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3622,7 +3625,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3633,10 +3636,10 @@
         <v>262</v>
       </c>
       <c r="C122" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3647,10 +3650,10 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3664,7 +3667,7 @@
         <v>262</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3675,10 +3678,10 @@
         <v>262</v>
       </c>
       <c r="C125" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3692,7 +3695,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3703,10 +3706,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3723,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3737,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3748,7 +3751,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3765,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3779,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3793,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3807,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3818,7 +3821,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3829,10 +3832,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3843,10 +3846,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3857,10 +3860,10 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3871,10 +3874,10 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3888,7 +3891,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3902,7 +3905,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3913,10 +3916,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,7 +3933,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3941,10 +3944,10 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3955,10 +3958,10 @@
         <v>260</v>
       </c>
       <c r="C145" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3969,10 +3972,10 @@
         <v>260</v>
       </c>
       <c r="C146" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3983,10 +3986,10 @@
         <v>260</v>
       </c>
       <c r="C147" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4000,7 +4003,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4014,7 +4017,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4025,10 +4028,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4042,7 +4045,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4053,10 +4056,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,7 +4073,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4084,7 +4087,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4098,7 +4101,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4112,7 +4115,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,7 +4129,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,7 +4143,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4151,10 +4154,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4168,7 +4171,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,7 +4185,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4193,10 +4196,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4210,7 +4213,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,7 +4227,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4238,7 +4241,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4252,7 +4255,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4266,7 +4269,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4283,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4297,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4308,7 +4311,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4322,7 +4325,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4339,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4350,7 +4353,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4364,7 +4367,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4375,10 +4378,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4392,7 +4395,7 @@
         <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4406,7 +4409,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,7 +4423,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4434,7 +4437,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4448,7 +4451,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4462,7 +4465,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4476,7 +4479,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4487,10 +4490,10 @@
         <v>261</v>
       </c>
       <c r="C183" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4501,10 +4504,10 @@
         <v>261</v>
       </c>
       <c r="C184" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4515,10 +4518,10 @@
         <v>261</v>
       </c>
       <c r="C185" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4529,10 +4532,10 @@
         <v>261</v>
       </c>
       <c r="C186" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4543,10 +4546,10 @@
         <v>261</v>
       </c>
       <c r="C187" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4557,10 +4560,10 @@
         <v>261</v>
       </c>
       <c r="C188" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4571,10 +4574,10 @@
         <v>261</v>
       </c>
       <c r="C189" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4585,10 +4588,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4599,10 +4602,10 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4613,10 +4616,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4630,7 +4633,7 @@
         <v>259</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4641,10 +4644,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4658,7 +4661,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4672,7 +4675,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4683,10 +4686,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4697,10 +4700,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4711,10 +4714,10 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,7 +4731,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4742,7 +4745,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4753,10 +4756,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,7 +4773,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4784,7 +4787,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4798,7 +4801,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,7 +4815,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4826,7 +4829,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4840,7 +4843,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4851,10 +4854,10 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4865,10 +4868,10 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4879,10 +4882,10 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4893,10 +4896,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4913,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4924,7 +4927,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4941,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4952,7 +4955,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4966,7 +4969,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4980,7 +4983,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4994,7 +4997,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5008,7 +5011,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5019,10 +5022,10 @@
         <v>261</v>
       </c>
       <c r="C221" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5033,10 +5036,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5050,7 +5053,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5061,10 +5064,10 @@
         <v>261</v>
       </c>
       <c r="C224" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5075,10 +5078,10 @@
         <v>261</v>
       </c>
       <c r="C225" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5089,10 +5092,10 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5106,7 +5109,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5117,10 +5120,10 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,7 +5137,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5145,10 +5148,10 @@
         <v>261</v>
       </c>
       <c r="C230" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5159,10 +5162,10 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5173,10 +5176,10 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5190,7 +5193,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5204,7 +5207,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5218,7 +5221,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5232,7 +5235,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5246,7 +5249,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5263,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5274,7 +5277,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5291,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5305,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5319,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5327,10 +5330,10 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5341,10 +5344,10 @@
         <v>261</v>
       </c>
       <c r="C244" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5355,10 +5358,10 @@
         <v>261</v>
       </c>
       <c r="C245" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5369,10 +5372,10 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5383,10 +5386,10 @@
         <v>261</v>
       </c>
       <c r="C247" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5397,10 +5400,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5411,10 +5414,10 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5425,10 +5428,10 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5442,7 +5445,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5453,10 +5456,10 @@
         <v>260</v>
       </c>
       <c r="C252" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5467,10 +5470,10 @@
         <v>260</v>
       </c>
       <c r="C253" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5481,10 +5484,10 @@
         <v>260</v>
       </c>
       <c r="C254" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5495,10 +5498,10 @@
         <v>260</v>
       </c>
       <c r="C255" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,7 +5515,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
   </sheetData>
